--- a/data/SCAMP_data_dictionary.xlsx
+++ b/data/SCAMP_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon.sharepoint.com/sites/MBTteam/Shared Documents/04. Data Management/Data Dictionaries/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5987" documentId="11_C1B2DE3178FB31C93C31E9A30ADCF2804E5FDF90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EFEB8AB-35F5-41B8-A287-4F77D287EF7D}"/>
+  <xr:revisionPtr revIDLastSave="6239" documentId="11_C1B2DE3178FB31C93C31E9A30ADCF2804E5FDF90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62CABC51-D15F-4C77-A22F-705B02AE18E1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="16440" tabRatio="792" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="792" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="10" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16740" uniqueCount="2883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18012" uniqueCount="3009">
   <si>
     <t>Instance</t>
   </si>
@@ -8247,150 +8247,6 @@
     <t>PM2_5_OUT_2018</t>
   </si>
   <si>
-    <t>Average NO2 exposure in 2013 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2014 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2015 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2016 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2017 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2018 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2013 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2014 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2015 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2016 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2017 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2018 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2013 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2014 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2015 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2016 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2017 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2018 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2013 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2014 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2015 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2016 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2017 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2018 (Instance 2 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2013 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2014 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2015 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2016 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2017 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average NO2 exposure in 2018 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2013 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2014 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2015 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2016 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2017 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average Ozone exposure in 2018 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2013 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2014 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2015 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2016 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2017 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM10 exposure in 2018 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2013 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2014 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2015 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2016 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2017 (Instance 1 address)</t>
-  </si>
-  <si>
-    <t>Average PM2.5 exposure in 2018 (Instance 1 address)</t>
-  </si>
-  <si>
     <t>lday_2013</t>
   </si>
   <si>
@@ -8466,153 +8322,6 @@
     <t>Noise pollution</t>
   </si>
   <si>
-    <t>Based on Instance 1 addresses in Year 2013, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2014, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2015, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2016, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2017, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2018, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2013, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2014, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2015, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2016, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2017, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2018, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2013, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2014, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2015, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2016, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2017, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2018, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2013, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2014, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2015, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2016, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2017, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 1 addresses in Year 2018, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2013, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2014, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2015, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2016, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2017, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2018, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2013, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2014, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2015, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2016, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2017, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2018, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2013, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2014, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2015, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2016, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2017, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2018, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2013, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2014, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2015, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2016, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2017, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Based on Instance 2 addresses in Year 2018, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
-  </si>
-  <si>
-    <t>Weighted average of exposure level at residential and school addresses</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Have you ever felt as if a double has taken the place of a family member friend or acquaintance?</t>
   </si>
   <si>
@@ -8695,6 +8404,675 @@
   </si>
   <si>
     <t>Over the last 2 weeks, how often have you been bothered by ? Feeling afraid as if something awful might happen</t>
+  </si>
+  <si>
+    <t>In 2013, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
+  </si>
+  <si>
+    <t>In 2014, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
+  </si>
+  <si>
+    <t>In 2015, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
+  </si>
+  <si>
+    <t>In 2016, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
+  </si>
+  <si>
+    <t>In 2017, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
+  </si>
+  <si>
+    <t>In 2018, a-weighted equivalent noise level over 12-hour day period (07:00-19:00), also known as the day noise indicator</t>
+  </si>
+  <si>
+    <t>In 2013, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
+  </si>
+  <si>
+    <t>In 2014, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
+  </si>
+  <si>
+    <t>In 2015, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
+  </si>
+  <si>
+    <t>In 2016, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
+  </si>
+  <si>
+    <t>In 2017, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
+  </si>
+  <si>
+    <t>In 2018, a-weighted equivalent noise level over 4-hour evening period (19:00-23:00), also known as the evening noise indicator</t>
+  </si>
+  <si>
+    <t>In 2013, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
+  </si>
+  <si>
+    <t>In 2014, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
+  </si>
+  <si>
+    <t>In 2015, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
+  </si>
+  <si>
+    <t>In 2016, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
+  </si>
+  <si>
+    <t>In 2017, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
+  </si>
+  <si>
+    <t>In 2018, a-weighted equivalent noise level over 8-hour night period (23:00-07:00), also known as the night noise indicator</t>
+  </si>
+  <si>
+    <t>In 2013, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
+  </si>
+  <si>
+    <t>In 2014, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
+  </si>
+  <si>
+    <t>In 2015, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
+  </si>
+  <si>
+    <t>In 2016, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
+  </si>
+  <si>
+    <t>In 2017, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
+  </si>
+  <si>
+    <t>In 2018, a-weighted equivalent noise level over a whole day, but with a penalty of +10dB(A) for night-time noise and +5 dB(A) for evening noise, also known as the day-evening-night noise indicator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average NO2 exposure in 2013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average NO2 exposure in 2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average NO2 exposure in 2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average NO2 exposure in 2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average NO2 exposure in 2017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average NO2 exposure in 2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Ozone exposure in 2013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Ozone exposure in 2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Ozone exposure in 2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Ozone exposure in 2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Ozone exposure in 2017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Ozone exposure in 2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM10 exposure in 2013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM10 exposure in 2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM10 exposure in 2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM10 exposure in 2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM10 exposure in 2017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM10 exposure in 2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM2.5 exposure in 2013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM2.5 exposure in 2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM2.5 exposure in 2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM2.5 exposure in 2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM2.5 exposure in 2017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average PM2.5 exposure in 2018 </t>
+  </si>
+  <si>
+    <t>Weighted average of exposure level at residential and school addresses (Instance 1)</t>
+  </si>
+  <si>
+    <t>Weighted average of exposure level at residential and school addresses (Instance 2)</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_50</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_100</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_250</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_500</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_50</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_100</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_250</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_500</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_50</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_100</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_250</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_500</t>
+  </si>
+  <si>
+    <t>tot_lowv_50</t>
+  </si>
+  <si>
+    <t>tot_lowv_100</t>
+  </si>
+  <si>
+    <t>tot_lowv_250</t>
+  </si>
+  <si>
+    <t>tot_lowv_500</t>
+  </si>
+  <si>
+    <t>tot_highv_50</t>
+  </si>
+  <si>
+    <t>tot_highv_100</t>
+  </si>
+  <si>
+    <t>tot_highv_250</t>
+  </si>
+  <si>
+    <t>tot_highv_500</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_50_24h</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_250_24h</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_50_24h</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_250_24h</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_50_24h</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_250_24h</t>
+  </si>
+  <si>
+    <t>tot_lowv_50_24h</t>
+  </si>
+  <si>
+    <t>tot_lowv_250_24h</t>
+  </si>
+  <si>
+    <t>tot_highv_50_24h</t>
+  </si>
+  <si>
+    <t>tot_highv_250_24h</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_100_24h</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_100_24h</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_100_24h</t>
+  </si>
+  <si>
+    <t>tot_lowv_100_24h</t>
+  </si>
+  <si>
+    <t>tot_highv_100_24h</t>
+  </si>
+  <si>
+    <t>tot_nat_spa_500_24h</t>
+  </si>
+  <si>
+    <t>tot_gre_spa_500_24h</t>
+  </si>
+  <si>
+    <t>tot_blu_spa_500_24h</t>
+  </si>
+  <si>
+    <t>tot_lowv_500_24h</t>
+  </si>
+  <si>
+    <t>tot_highv_500_24h</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 50m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 100m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 250m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 500m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 50m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 100m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 250m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 500m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 50m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 100m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 250m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 500m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 50m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 100m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 250m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 500m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 50m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 100m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 250m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 500m buffer (daytime weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 50m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 100m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 250m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of total natural space in 500m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 50m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 100m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 250m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of greenspace in 500m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 50m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 100m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 250m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of blue space in 500m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 50m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 100m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 250m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of grassland in 500m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 50m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 100m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 250m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Daily exposure rate of woodland in 500m buffer (full-day weighting)</t>
+  </si>
+  <si>
+    <t>Natural environment</t>
+  </si>
+  <si>
+    <t>Tissue</t>
+  </si>
+  <si>
+    <t>Integrative</t>
+  </si>
+  <si>
+    <t>BAN</t>
+  </si>
+  <si>
+    <t>BAN_torso</t>
+  </si>
+  <si>
+    <t>BAN_head</t>
+  </si>
+  <si>
+    <t>BAN_legs</t>
+  </si>
+  <si>
+    <t>phone_nearhead_2G</t>
+  </si>
+  <si>
+    <t>phone_nearhead_3G</t>
+  </si>
+  <si>
+    <t>dect_nearhead</t>
+  </si>
+  <si>
+    <t>phone_headset</t>
+  </si>
+  <si>
+    <t>phone_data</t>
+  </si>
+  <si>
+    <t>phdata_fronteye20</t>
+  </si>
+  <si>
+    <t>phdata_fronteye30</t>
+  </si>
+  <si>
+    <t>phdata_frontbelly20</t>
+  </si>
+  <si>
+    <t>phdata_frontbelly30</t>
+  </si>
+  <si>
+    <t>phdata_frontbellyhor</t>
+  </si>
+  <si>
+    <t>phdata_frontabovelegs</t>
+  </si>
+  <si>
+    <t>laptop</t>
+  </si>
+  <si>
+    <t>onnear</t>
+  </si>
+  <si>
+    <t>smartwatch</t>
+  </si>
+  <si>
+    <t>tablet</t>
+  </si>
+  <si>
+    <t>tab_fronteye20</t>
+  </si>
+  <si>
+    <t>tab_fronteye30</t>
+  </si>
+  <si>
+    <t>tab_frontbelly20</t>
+  </si>
+  <si>
+    <t>tab_frontbelly30</t>
+  </si>
+  <si>
+    <t>tab_frontbellyhor</t>
+  </si>
+  <si>
+    <t>tab_frontabovelegs</t>
+  </si>
+  <si>
+    <t>VR</t>
+  </si>
+  <si>
+    <t>wifirouter</t>
+  </si>
+  <si>
+    <t>far_overall_fm</t>
+  </si>
+  <si>
+    <t>far_overall_tv</t>
+  </si>
+  <si>
+    <t>far_overall_800dl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">far_overall_800ul </t>
+  </si>
+  <si>
+    <t>far_overall_900ul</t>
+  </si>
+  <si>
+    <t>far_overall_900dl</t>
+  </si>
+  <si>
+    <t>far_overall_1800ul</t>
+  </si>
+  <si>
+    <t>far_overall_1800dl</t>
+  </si>
+  <si>
+    <t>far_overall_dect</t>
+  </si>
+  <si>
+    <t>far_overall_2100ul</t>
+  </si>
+  <si>
+    <t>far_overall_2100dl</t>
+  </si>
+  <si>
+    <t>far_overall_wifi2</t>
+  </si>
+  <si>
+    <t>far_overall_2600ul</t>
+  </si>
+  <si>
+    <t>far_overall_2600dl</t>
+  </si>
+  <si>
+    <t>far_overall_wimax</t>
+  </si>
+  <si>
+    <t>far_overall_wifi5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tissue, organ or body part which the dose estimate applies to </t>
+  </si>
+  <si>
+    <t>Total exposure resulting from a socalled body area network (here abbreviated to BAN). This is a wireless network with sensor components (wearables) attached to torso, head and/or legs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from the torso component of a BAN </t>
+  </si>
+  <si>
+    <t>Exposure resulting from the head component of a BAN</t>
+  </si>
+  <si>
+    <t>Exposure resulting from the leg component of a BAN</t>
+  </si>
+  <si>
+    <t>Exposure resulting from holding a mobile phone next to the head on network calls on the 2G network</t>
+  </si>
+  <si>
+    <t>Exposure resulting from holding a mobile phone next to the head on network calls on the 3G or 4G network (combined)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from holding a DECT phone (cordless phone) near the head </t>
+  </si>
+  <si>
+    <t>Exposure resulting from a network call, but while using headset, earphone and Bluetooth devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from data use through the mobile network, or from using data through Wi-Fi. </t>
+  </si>
+  <si>
+    <t>Exposure resulting from internet calls and from data use through the mobile network, or from using data through Wi-Fi, where the phone is held at a 20 cm distance from the face</t>
+  </si>
+  <si>
+    <t>Exposure resulting from internet calls and from data use through the mobile network, or from using data through Wi-Fi, where the phone is held at a 30 cm distance from the face</t>
+  </si>
+  <si>
+    <t>Total exposure to the specified tissue from all sources combined (mJ/kg/day, applied to all RF-EMF exposure estimates)</t>
+  </si>
+  <si>
+    <t>Exposure resulting from internet calls and from data use through the mobile network, or from using data through Wi-Fi, where the phone is held at a 20 cm distance from the abdomen</t>
+  </si>
+  <si>
+    <t>Exposure resulting from internet calls and from data use through the mobile network, or from using data through Wi-Fi, where the phone is held at a 30 cm distance from the abdomen</t>
+  </si>
+  <si>
+    <t>Exposure resulting from internet calls and from data use through the mobile network, or from using data through Wi-Fi, where the phone is resting on a surface horizontally</t>
+  </si>
+  <si>
+    <t>Exposure resulting from laptop use (presumably connected to the internet, and laptop on the table)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from typical standby traffic happening when the phone is carried on or near the body (e.g. in pockets when at school, travelling or at home) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from wearing a smartwatch on the wrist </t>
+  </si>
+  <si>
+    <t>Exposure resulting from tablet use, presumably connected to the internet</t>
+  </si>
+  <si>
+    <t>Exposure resulting from tablet use, presumably connected to the internet, where the tablet is held at a 20 cm distance from the eye</t>
+  </si>
+  <si>
+    <t>Exposure resulting from tablet use, presumably connected to the internet, where the tablet is held at a 30 cm distance from the eye</t>
+  </si>
+  <si>
+    <t>Exposure resulting from tablet use, presumably connected to the internet, where the tablet is held at a 20 cm distance from the abdomen</t>
+  </si>
+  <si>
+    <t>Exposure resulting from tablet use, presumably connected to the internet, where the tablet is held at a 30 cm distance from the abdomen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from tablet use, presumably connected to the internet, where the tablet is resting on a surface horizontally. </t>
+  </si>
+  <si>
+    <t>Exposure resulting from internet calls and from data use through the mobile network, or from using data through Wi-Fi, where the phone is resting on the upper legs while seated</t>
+  </si>
+  <si>
+    <t>Exposure resulting from tablet use, presumably connected to the internet, where the tablet is resting on the upper legs while seated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from virtual reality goggles </t>
+  </si>
+  <si>
+    <t>Exposure resulting from having a Wi-Fi router in the room</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to FM broadcast band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from far-field exposure to TV broadcast band </t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 800 DL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 800 UL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 900 UL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 900 DL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 1800 UL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 1800 DL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 2100 UL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 2100 DL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 2600 UL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to 2600 DL band</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to the DECT band (1880-1900 MHz)</t>
+  </si>
+  <si>
+    <t>Exposure resulting from far-field exposure to Wi-Fi 2.4 GHz band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from far-field exposure to WiMax band, assumed to be zero because not used a lot and could not be reliably estimated by ExpoM-RF measurements. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure resulting from far-field exposure to Wi-Fi 5 GHz band, assumed (based on spot measurements) to be equal to Wi-Fi 2.4 GHz band. </t>
+  </si>
+  <si>
+    <t>RF-EMF exposure estimates are available across 64 tissues in each participant</t>
+  </si>
+  <si>
+    <t>RF-EMF</t>
   </si>
 </sst>
 </file>
@@ -16565,7 +16943,7 @@
         <v>53</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>2856</v>
+        <v>2759</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>639</v>
@@ -16594,7 +16972,7 @@
         <v>53</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>2857</v>
+        <v>2760</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>639</v>
@@ -16623,7 +17001,7 @@
         <v>53</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>2858</v>
+        <v>2761</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>639</v>
@@ -16652,7 +17030,7 @@
         <v>53</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>2859</v>
+        <v>2762</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>639</v>
@@ -16681,7 +17059,7 @@
         <v>53</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>2860</v>
+        <v>2763</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>639</v>
@@ -16710,7 +17088,7 @@
         <v>53</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>2861</v>
+        <v>2764</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>639</v>
@@ -16739,7 +17117,7 @@
         <v>53</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>2862</v>
+        <v>2765</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>639</v>
@@ -16768,7 +17146,7 @@
         <v>53</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>2863</v>
+        <v>2766</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>636</v>
@@ -16797,7 +17175,7 @@
         <v>53</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>2864</v>
+        <v>2767</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>639</v>
@@ -26750,7 +27128,7 @@
         <v>53</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>2865</v>
+        <v>2768</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>636</v>
@@ -26779,7 +27157,7 @@
         <v>53</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>2856</v>
+        <v>2759</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>639</v>
@@ -26808,7 +27186,7 @@
         <v>53</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>2857</v>
+        <v>2760</v>
       </c>
       <c r="E599" s="1" t="s">
         <v>639</v>
@@ -26837,7 +27215,7 @@
         <v>53</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>2858</v>
+        <v>2761</v>
       </c>
       <c r="E600" s="1" t="s">
         <v>639</v>
@@ -26866,7 +27244,7 @@
         <v>53</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>2859</v>
+        <v>2762</v>
       </c>
       <c r="E601" s="1" t="s">
         <v>639</v>
@@ -26895,7 +27273,7 @@
         <v>53</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>2860</v>
+        <v>2763</v>
       </c>
       <c r="E602" s="1" t="s">
         <v>639</v>
@@ -26924,7 +27302,7 @@
         <v>53</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>2861</v>
+        <v>2764</v>
       </c>
       <c r="E603" s="1" t="s">
         <v>639</v>
@@ -26953,7 +27331,7 @@
         <v>53</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>2862</v>
+        <v>2765</v>
       </c>
       <c r="E604" s="1" t="s">
         <v>639</v>
@@ -26982,7 +27360,7 @@
         <v>53</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>2863</v>
+        <v>2766</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>636</v>
@@ -27011,7 +27389,7 @@
         <v>53</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>2864</v>
+        <v>2767</v>
       </c>
       <c r="E606" s="1" t="s">
         <v>639</v>
@@ -28376,7 +28754,7 @@
         <v>53</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>2876</v>
+        <v>2779</v>
       </c>
       <c r="E654" s="1" t="s">
         <v>996</v>
@@ -28408,7 +28786,7 @@
         <v>53</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>2877</v>
+        <v>2780</v>
       </c>
       <c r="E655" s="1" t="s">
         <v>996</v>
@@ -28440,7 +28818,7 @@
         <v>53</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>2878</v>
+        <v>2781</v>
       </c>
       <c r="E656" s="1" t="s">
         <v>996</v>
@@ -28472,7 +28850,7 @@
         <v>53</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>2879</v>
+        <v>2782</v>
       </c>
       <c r="E657" s="1" t="s">
         <v>996</v>
@@ -28504,7 +28882,7 @@
         <v>53</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>2880</v>
+        <v>2783</v>
       </c>
       <c r="E658" s="1" t="s">
         <v>996</v>
@@ -28536,7 +28914,7 @@
         <v>53</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>2881</v>
+        <v>2784</v>
       </c>
       <c r="E659" s="1" t="s">
         <v>996</v>
@@ -28568,7 +28946,7 @@
         <v>53</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>2882</v>
+        <v>2785</v>
       </c>
       <c r="E660" s="1" t="s">
         <v>996</v>
@@ -28600,7 +28978,7 @@
         <v>53</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>2866</v>
+        <v>2769</v>
       </c>
       <c r="E661" s="1" t="s">
         <v>996</v>
@@ -28632,7 +29010,7 @@
         <v>53</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>2867</v>
+        <v>2770</v>
       </c>
       <c r="E662" s="1" t="s">
         <v>996</v>
@@ -28664,7 +29042,7 @@
         <v>53</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>2868</v>
+        <v>2771</v>
       </c>
       <c r="E663" s="1" t="s">
         <v>996</v>
@@ -28696,7 +29074,7 @@
         <v>53</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>2869</v>
+        <v>2772</v>
       </c>
       <c r="E664" s="1" t="s">
         <v>996</v>
@@ -28728,7 +29106,7 @@
         <v>53</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>2870</v>
+        <v>2773</v>
       </c>
       <c r="E665" s="1" t="s">
         <v>996</v>
@@ -28760,7 +29138,7 @@
         <v>53</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>2871</v>
+        <v>2774</v>
       </c>
       <c r="E666" s="1" t="s">
         <v>996</v>
@@ -28792,7 +29170,7 @@
         <v>53</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>2872</v>
+        <v>2775</v>
       </c>
       <c r="E667" s="1" t="s">
         <v>996</v>
@@ -28824,7 +29202,7 @@
         <v>53</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>2873</v>
+        <v>2776</v>
       </c>
       <c r="E668" s="1" t="s">
         <v>996</v>
@@ -28856,7 +29234,7 @@
         <v>53</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>2874</v>
+        <v>2777</v>
       </c>
       <c r="E669" s="1" t="s">
         <v>996</v>
@@ -38614,7 +38992,7 @@
         <v>53</v>
       </c>
       <c r="D1004" t="s">
-        <v>2866</v>
+        <v>2769</v>
       </c>
       <c r="E1004" t="s">
         <v>996</v>
@@ -38643,7 +39021,7 @@
         <v>53</v>
       </c>
       <c r="D1005" t="s">
-        <v>2867</v>
+        <v>2770</v>
       </c>
       <c r="E1005" t="s">
         <v>996</v>
@@ -38672,7 +39050,7 @@
         <v>53</v>
       </c>
       <c r="D1006" t="s">
-        <v>2875</v>
+        <v>2778</v>
       </c>
       <c r="E1006" t="s">
         <v>996</v>
@@ -38701,7 +39079,7 @@
         <v>53</v>
       </c>
       <c r="D1007" t="s">
-        <v>2869</v>
+        <v>2772</v>
       </c>
       <c r="E1007" t="s">
         <v>996</v>
@@ -38730,7 +39108,7 @@
         <v>53</v>
       </c>
       <c r="D1008" t="s">
-        <v>2870</v>
+        <v>2773</v>
       </c>
       <c r="E1008" t="s">
         <v>996</v>
@@ -38759,7 +39137,7 @@
         <v>53</v>
       </c>
       <c r="D1009" t="s">
-        <v>2871</v>
+        <v>2774</v>
       </c>
       <c r="E1009" t="s">
         <v>996</v>
@@ -38788,7 +39166,7 @@
         <v>53</v>
       </c>
       <c r="D1010" s="1" t="s">
-        <v>2872</v>
+        <v>2775</v>
       </c>
       <c r="E1010" t="s">
         <v>996</v>
@@ -38817,7 +39195,7 @@
         <v>53</v>
       </c>
       <c r="D1011" s="1" t="s">
-        <v>2873</v>
+        <v>2776</v>
       </c>
       <c r="E1011" t="s">
         <v>996</v>
@@ -38846,7 +39224,7 @@
         <v>53</v>
       </c>
       <c r="D1012" t="s">
-        <v>2876</v>
+        <v>2779</v>
       </c>
       <c r="E1012" t="s">
         <v>996</v>
@@ -38875,7 +39253,7 @@
         <v>53</v>
       </c>
       <c r="D1013" t="s">
-        <v>2877</v>
+        <v>2780</v>
       </c>
       <c r="E1013" t="s">
         <v>996</v>
@@ -38904,7 +39282,7 @@
         <v>53</v>
       </c>
       <c r="D1014" t="s">
-        <v>2878</v>
+        <v>2781</v>
       </c>
       <c r="E1014" t="s">
         <v>996</v>
@@ -38933,7 +39311,7 @@
         <v>53</v>
       </c>
       <c r="D1015" t="s">
-        <v>2879</v>
+        <v>2782</v>
       </c>
       <c r="E1015" t="s">
         <v>996</v>
@@ -38962,7 +39340,7 @@
         <v>53</v>
       </c>
       <c r="D1016" t="s">
-        <v>2880</v>
+        <v>2783</v>
       </c>
       <c r="E1016" t="s">
         <v>996</v>
@@ -38991,7 +39369,7 @@
         <v>53</v>
       </c>
       <c r="D1017" t="s">
-        <v>2881</v>
+        <v>2784</v>
       </c>
       <c r="E1017" t="s">
         <v>996</v>
@@ -39020,7 +39398,7 @@
         <v>53</v>
       </c>
       <c r="D1018" t="s">
-        <v>2882</v>
+        <v>2785</v>
       </c>
       <c r="E1018" t="s">
         <v>996</v>
@@ -49487,7 +49865,7 @@
         <v>53</v>
       </c>
       <c r="D1364" t="s">
-        <v>2866</v>
+        <v>2769</v>
       </c>
       <c r="E1364" t="s">
         <v>996</v>
@@ -49516,7 +49894,7 @@
         <v>53</v>
       </c>
       <c r="D1365" t="s">
-        <v>2867</v>
+        <v>2770</v>
       </c>
       <c r="E1365" t="s">
         <v>996</v>
@@ -49545,7 +49923,7 @@
         <v>53</v>
       </c>
       <c r="D1366" t="s">
-        <v>2875</v>
+        <v>2778</v>
       </c>
       <c r="E1366" t="s">
         <v>996</v>
@@ -49574,7 +49952,7 @@
         <v>53</v>
       </c>
       <c r="D1367" t="s">
-        <v>2869</v>
+        <v>2772</v>
       </c>
       <c r="E1367" t="s">
         <v>996</v>
@@ -49603,7 +49981,7 @@
         <v>53</v>
       </c>
       <c r="D1368" t="s">
-        <v>2870</v>
+        <v>2773</v>
       </c>
       <c r="E1368" t="s">
         <v>996</v>
@@ -49632,7 +50010,7 @@
         <v>53</v>
       </c>
       <c r="D1369" t="s">
-        <v>2871</v>
+        <v>2774</v>
       </c>
       <c r="E1369" t="s">
         <v>996</v>
@@ -49661,7 +50039,7 @@
         <v>53</v>
       </c>
       <c r="D1370" s="1" t="s">
-        <v>2872</v>
+        <v>2775</v>
       </c>
       <c r="E1370" t="s">
         <v>996</v>
@@ -49690,7 +50068,7 @@
         <v>53</v>
       </c>
       <c r="D1371" s="1" t="s">
-        <v>2873</v>
+        <v>2776</v>
       </c>
       <c r="E1371" t="s">
         <v>996</v>
@@ -49719,7 +50097,7 @@
         <v>53</v>
       </c>
       <c r="D1372" t="s">
-        <v>2876</v>
+        <v>2779</v>
       </c>
       <c r="E1372" t="s">
         <v>996</v>
@@ -49748,7 +50126,7 @@
         <v>53</v>
       </c>
       <c r="D1373" t="s">
-        <v>2877</v>
+        <v>2780</v>
       </c>
       <c r="E1373" t="s">
         <v>996</v>
@@ -49777,7 +50155,7 @@
         <v>53</v>
       </c>
       <c r="D1374" t="s">
-        <v>2878</v>
+        <v>2781</v>
       </c>
       <c r="E1374" t="s">
         <v>996</v>
@@ -49806,7 +50184,7 @@
         <v>53</v>
       </c>
       <c r="D1375" t="s">
-        <v>2879</v>
+        <v>2782</v>
       </c>
       <c r="E1375" t="s">
         <v>996</v>
@@ -49838,7 +50216,7 @@
         <v>53</v>
       </c>
       <c r="D1376" t="s">
-        <v>2880</v>
+        <v>2783</v>
       </c>
       <c r="E1376" t="s">
         <v>996</v>
@@ -49867,7 +50245,7 @@
         <v>53</v>
       </c>
       <c r="D1377" t="s">
-        <v>2881</v>
+        <v>2784</v>
       </c>
       <c r="E1377" t="s">
         <v>996</v>
@@ -49899,7 +50277,7 @@
         <v>53</v>
       </c>
       <c r="D1378" t="s">
-        <v>2882</v>
+        <v>2785</v>
       </c>
       <c r="E1378" t="s">
         <v>996</v>
@@ -55693,7 +56071,7 @@
         <v>53</v>
       </c>
       <c r="D1572" t="s">
-        <v>2866</v>
+        <v>2769</v>
       </c>
       <c r="E1572" t="s">
         <v>996</v>
@@ -55722,7 +56100,7 @@
         <v>53</v>
       </c>
       <c r="D1573" t="s">
-        <v>2867</v>
+        <v>2770</v>
       </c>
       <c r="E1573" t="s">
         <v>996</v>
@@ -55751,7 +56129,7 @@
         <v>53</v>
       </c>
       <c r="D1574" t="s">
-        <v>2875</v>
+        <v>2778</v>
       </c>
       <c r="E1574" t="s">
         <v>996</v>
@@ -55780,7 +56158,7 @@
         <v>53</v>
       </c>
       <c r="D1575" t="s">
-        <v>2869</v>
+        <v>2772</v>
       </c>
       <c r="E1575" t="s">
         <v>996</v>
@@ -55809,7 +56187,7 @@
         <v>53</v>
       </c>
       <c r="D1576" t="s">
-        <v>2870</v>
+        <v>2773</v>
       </c>
       <c r="E1576" t="s">
         <v>996</v>
@@ -55838,7 +56216,7 @@
         <v>53</v>
       </c>
       <c r="D1577" t="s">
-        <v>2871</v>
+        <v>2774</v>
       </c>
       <c r="E1577" t="s">
         <v>996</v>
@@ -55867,7 +56245,7 @@
         <v>53</v>
       </c>
       <c r="D1578" s="1" t="s">
-        <v>2872</v>
+        <v>2775</v>
       </c>
       <c r="E1578" t="s">
         <v>996</v>
@@ -55896,7 +56274,7 @@
         <v>53</v>
       </c>
       <c r="D1579" s="1" t="s">
-        <v>2873</v>
+        <v>2776</v>
       </c>
       <c r="E1579" t="s">
         <v>996</v>
@@ -55925,7 +56303,7 @@
         <v>53</v>
       </c>
       <c r="D1580" t="s">
-        <v>2876</v>
+        <v>2779</v>
       </c>
       <c r="E1580" t="s">
         <v>996</v>
@@ -55954,7 +56332,7 @@
         <v>53</v>
       </c>
       <c r="D1581" t="s">
-        <v>2877</v>
+        <v>2780</v>
       </c>
       <c r="E1581" t="s">
         <v>996</v>
@@ -55983,7 +56361,7 @@
         <v>53</v>
       </c>
       <c r="D1582" t="s">
-        <v>2878</v>
+        <v>2781</v>
       </c>
       <c r="E1582" t="s">
         <v>996</v>
@@ -56012,7 +56390,7 @@
         <v>53</v>
       </c>
       <c r="D1583" t="s">
-        <v>2879</v>
+        <v>2782</v>
       </c>
       <c r="E1583" t="s">
         <v>996</v>
@@ -56041,7 +56419,7 @@
         <v>53</v>
       </c>
       <c r="D1584" t="s">
-        <v>2880</v>
+        <v>2783</v>
       </c>
       <c r="E1584" t="s">
         <v>996</v>
@@ -56070,7 +56448,7 @@
         <v>53</v>
       </c>
       <c r="D1585" t="s">
-        <v>2881</v>
+        <v>2784</v>
       </c>
       <c r="E1585" t="s">
         <v>996</v>
@@ -56099,7 +56477,7 @@
         <v>53</v>
       </c>
       <c r="D1586" t="s">
-        <v>2882</v>
+        <v>2785</v>
       </c>
       <c r="E1586" t="s">
         <v>996</v>
@@ -56476,7 +56854,7 @@
         <v>53</v>
       </c>
       <c r="D1599" t="s">
-        <v>2855</v>
+        <v>2758</v>
       </c>
       <c r="E1599" t="s">
         <v>1918</v>
@@ -62177,7 +62555,7 @@
         <v>53</v>
       </c>
       <c r="D1799" t="s">
-        <v>2866</v>
+        <v>2769</v>
       </c>
       <c r="E1799" t="s">
         <v>996</v>
@@ -62206,7 +62584,7 @@
         <v>53</v>
       </c>
       <c r="D1800" t="s">
-        <v>2867</v>
+        <v>2770</v>
       </c>
       <c r="E1800" t="s">
         <v>996</v>
@@ -62235,7 +62613,7 @@
         <v>53</v>
       </c>
       <c r="D1801" t="s">
-        <v>2875</v>
+        <v>2778</v>
       </c>
       <c r="E1801" t="s">
         <v>996</v>
@@ -62264,7 +62642,7 @@
         <v>53</v>
       </c>
       <c r="D1802" t="s">
-        <v>2869</v>
+        <v>2772</v>
       </c>
       <c r="E1802" t="s">
         <v>996</v>
@@ -62293,7 +62671,7 @@
         <v>53</v>
       </c>
       <c r="D1803" t="s">
-        <v>2870</v>
+        <v>2773</v>
       </c>
       <c r="E1803" t="s">
         <v>996</v>
@@ -62322,7 +62700,7 @@
         <v>53</v>
       </c>
       <c r="D1804" t="s">
-        <v>2871</v>
+        <v>2774</v>
       </c>
       <c r="E1804" t="s">
         <v>996</v>
@@ -62351,7 +62729,7 @@
         <v>53</v>
       </c>
       <c r="D1805" s="1" t="s">
-        <v>2872</v>
+        <v>2775</v>
       </c>
       <c r="E1805" t="s">
         <v>996</v>
@@ -62380,7 +62758,7 @@
         <v>53</v>
       </c>
       <c r="D1806" s="1" t="s">
-        <v>2873</v>
+        <v>2776</v>
       </c>
       <c r="E1806" t="s">
         <v>996</v>
@@ -62409,7 +62787,7 @@
         <v>53</v>
       </c>
       <c r="D1807" t="s">
-        <v>2876</v>
+        <v>2779</v>
       </c>
       <c r="E1807" t="s">
         <v>996</v>
@@ -62438,7 +62816,7 @@
         <v>53</v>
       </c>
       <c r="D1808" t="s">
-        <v>2877</v>
+        <v>2780</v>
       </c>
       <c r="E1808" t="s">
         <v>996</v>
@@ -62467,7 +62845,7 @@
         <v>53</v>
       </c>
       <c r="D1809" t="s">
-        <v>2878</v>
+        <v>2781</v>
       </c>
       <c r="E1809" t="s">
         <v>996</v>
@@ -62496,7 +62874,7 @@
         <v>53</v>
       </c>
       <c r="D1810" t="s">
-        <v>2879</v>
+        <v>2782</v>
       </c>
       <c r="E1810" t="s">
         <v>996</v>
@@ -62525,7 +62903,7 @@
         <v>53</v>
       </c>
       <c r="D1811" t="s">
-        <v>2880</v>
+        <v>2783</v>
       </c>
       <c r="E1811" t="s">
         <v>996</v>
@@ -62554,7 +62932,7 @@
         <v>53</v>
       </c>
       <c r="D1812" t="s">
-        <v>2881</v>
+        <v>2784</v>
       </c>
       <c r="E1812" t="s">
         <v>996</v>
@@ -62583,7 +62961,7 @@
         <v>53</v>
       </c>
       <c r="D1813" t="s">
-        <v>2882</v>
+        <v>2785</v>
       </c>
       <c r="E1813" t="s">
         <v>996</v>
@@ -63163,7 +63541,7 @@
         <v>53</v>
       </c>
       <c r="D1833" t="s">
-        <v>2855</v>
+        <v>2758</v>
       </c>
       <c r="E1833" t="s">
         <v>1918</v>
@@ -67955,14 +68333,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE32096-AFA2-4F60-8570-02C22160DF48}">
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I267"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="209.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="176.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -68010,10 +68388,10 @@
         <v>891</v>
       </c>
       <c r="D2" t="s">
-        <v>2757</v>
+        <v>2810</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -68039,10 +68417,10 @@
         <v>891</v>
       </c>
       <c r="D3" t="s">
-        <v>2758</v>
+        <v>2811</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
@@ -68068,10 +68446,10 @@
         <v>891</v>
       </c>
       <c r="D4" t="s">
-        <v>2759</v>
+        <v>2812</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F4" t="s">
         <v>6</v>
@@ -68097,10 +68475,10 @@
         <v>891</v>
       </c>
       <c r="D5" t="s">
-        <v>2760</v>
+        <v>2813</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -68126,10 +68504,10 @@
         <v>891</v>
       </c>
       <c r="D6" t="s">
-        <v>2761</v>
+        <v>2814</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -68155,10 +68533,10 @@
         <v>891</v>
       </c>
       <c r="D7" t="s">
-        <v>2762</v>
+        <v>2815</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -68184,10 +68562,10 @@
         <v>891</v>
       </c>
       <c r="D8" t="s">
-        <v>2763</v>
+        <v>2816</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -68213,10 +68591,10 @@
         <v>891</v>
       </c>
       <c r="D9" t="s">
-        <v>2764</v>
+        <v>2817</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
@@ -68242,10 +68620,10 @@
         <v>891</v>
       </c>
       <c r="D10" t="s">
-        <v>2765</v>
+        <v>2818</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
@@ -68271,10 +68649,10 @@
         <v>891</v>
       </c>
       <c r="D11" t="s">
-        <v>2766</v>
+        <v>2819</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F11" t="s">
         <v>6</v>
@@ -68300,10 +68678,10 @@
         <v>891</v>
       </c>
       <c r="D12" t="s">
-        <v>2767</v>
+        <v>2820</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F12" t="s">
         <v>6</v>
@@ -68329,10 +68707,10 @@
         <v>891</v>
       </c>
       <c r="D13" t="s">
-        <v>2768</v>
+        <v>2821</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -68358,10 +68736,10 @@
         <v>891</v>
       </c>
       <c r="D14" t="s">
-        <v>2769</v>
+        <v>2822</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F14" t="s">
         <v>6</v>
@@ -68387,10 +68765,10 @@
         <v>891</v>
       </c>
       <c r="D15" t="s">
-        <v>2770</v>
+        <v>2823</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F15" t="s">
         <v>6</v>
@@ -68416,10 +68794,10 @@
         <v>891</v>
       </c>
       <c r="D16" t="s">
-        <v>2771</v>
+        <v>2824</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F16" t="s">
         <v>6</v>
@@ -68445,10 +68823,10 @@
         <v>891</v>
       </c>
       <c r="D17" t="s">
-        <v>2772</v>
+        <v>2825</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F17" t="s">
         <v>6</v>
@@ -68474,10 +68852,10 @@
         <v>891</v>
       </c>
       <c r="D18" t="s">
-        <v>2773</v>
+        <v>2826</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F18" t="s">
         <v>6</v>
@@ -68503,10 +68881,10 @@
         <v>891</v>
       </c>
       <c r="D19" t="s">
-        <v>2774</v>
+        <v>2827</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F19" t="s">
         <v>6</v>
@@ -68532,10 +68910,10 @@
         <v>891</v>
       </c>
       <c r="D20" t="s">
-        <v>2775</v>
+        <v>2828</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F20" t="s">
         <v>6</v>
@@ -68561,10 +68939,10 @@
         <v>891</v>
       </c>
       <c r="D21" t="s">
-        <v>2776</v>
+        <v>2829</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F21" t="s">
         <v>6</v>
@@ -68590,10 +68968,10 @@
         <v>891</v>
       </c>
       <c r="D22" t="s">
-        <v>2777</v>
+        <v>2830</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F22" t="s">
         <v>6</v>
@@ -68619,10 +68997,10 @@
         <v>891</v>
       </c>
       <c r="D23" t="s">
-        <v>2778</v>
+        <v>2831</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
@@ -68648,10 +69026,10 @@
         <v>891</v>
       </c>
       <c r="D24" t="s">
-        <v>2779</v>
+        <v>2832</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F24" t="s">
         <v>6</v>
@@ -68677,10 +69055,10 @@
         <v>891</v>
       </c>
       <c r="D25" t="s">
-        <v>2780</v>
+        <v>2833</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F25" t="s">
         <v>6</v>
@@ -68697,7 +69075,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2781</v>
+        <v>2733</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -68706,10 +69084,10 @@
         <v>891</v>
       </c>
       <c r="D26" t="s">
-        <v>2806</v>
+        <v>2786</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F26" t="s">
         <v>6</v>
@@ -68721,12 +69099,12 @@
         <v>2708</v>
       </c>
       <c r="I26" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2782</v>
+        <v>2734</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -68735,10 +69113,10 @@
         <v>891</v>
       </c>
       <c r="D27" t="s">
-        <v>2807</v>
+        <v>2787</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F27" t="s">
         <v>6</v>
@@ -68750,12 +69128,12 @@
         <v>2708</v>
       </c>
       <c r="I27" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2783</v>
+        <v>2735</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -68764,10 +69142,10 @@
         <v>891</v>
       </c>
       <c r="D28" t="s">
-        <v>2808</v>
+        <v>2788</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F28" t="s">
         <v>6</v>
@@ -68779,12 +69157,12 @@
         <v>2708</v>
       </c>
       <c r="I28" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2784</v>
+        <v>2736</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -68793,10 +69171,10 @@
         <v>891</v>
       </c>
       <c r="D29" t="s">
-        <v>2809</v>
+        <v>2789</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F29" t="s">
         <v>6</v>
@@ -68808,12 +69186,12 @@
         <v>2708</v>
       </c>
       <c r="I29" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2785</v>
+        <v>2737</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -68822,10 +69200,10 @@
         <v>891</v>
       </c>
       <c r="D30" t="s">
-        <v>2810</v>
+        <v>2790</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F30" t="s">
         <v>6</v>
@@ -68837,12 +69215,12 @@
         <v>2708</v>
       </c>
       <c r="I30" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2786</v>
+        <v>2738</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -68851,10 +69229,10 @@
         <v>891</v>
       </c>
       <c r="D31" t="s">
-        <v>2811</v>
+        <v>2791</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F31" t="s">
         <v>6</v>
@@ -68866,12 +69244,12 @@
         <v>2708</v>
       </c>
       <c r="I31" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2787</v>
+        <v>2739</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -68880,10 +69258,10 @@
         <v>891</v>
       </c>
       <c r="D32" t="s">
-        <v>2812</v>
+        <v>2792</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F32" t="s">
         <v>6</v>
@@ -68895,12 +69273,12 @@
         <v>2708</v>
       </c>
       <c r="I32" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2788</v>
+        <v>2740</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -68909,10 +69287,10 @@
         <v>891</v>
       </c>
       <c r="D33" t="s">
-        <v>2813</v>
+        <v>2793</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F33" t="s">
         <v>6</v>
@@ -68924,12 +69302,12 @@
         <v>2708</v>
       </c>
       <c r="I33" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2789</v>
+        <v>2741</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -68938,10 +69316,10 @@
         <v>891</v>
       </c>
       <c r="D34" t="s">
-        <v>2814</v>
+        <v>2794</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F34" t="s">
         <v>6</v>
@@ -68953,12 +69331,12 @@
         <v>2708</v>
       </c>
       <c r="I34" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2790</v>
+        <v>2742</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -68967,10 +69345,10 @@
         <v>891</v>
       </c>
       <c r="D35" t="s">
-        <v>2815</v>
+        <v>2795</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F35" t="s">
         <v>6</v>
@@ -68982,12 +69360,12 @@
         <v>2708</v>
       </c>
       <c r="I35" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2791</v>
+        <v>2743</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -68996,10 +69374,10 @@
         <v>891</v>
       </c>
       <c r="D36" t="s">
-        <v>2816</v>
+        <v>2796</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F36" t="s">
         <v>6</v>
@@ -69011,12 +69389,12 @@
         <v>2708</v>
       </c>
       <c r="I36" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>2792</v>
+        <v>2744</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -69025,10 +69403,10 @@
         <v>891</v>
       </c>
       <c r="D37" t="s">
-        <v>2817</v>
+        <v>2797</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F37" t="s">
         <v>6</v>
@@ -69040,12 +69418,12 @@
         <v>2708</v>
       </c>
       <c r="I37" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>2793</v>
+        <v>2745</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -69054,10 +69432,10 @@
         <v>891</v>
       </c>
       <c r="D38" t="s">
-        <v>2818</v>
+        <v>2798</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F38" t="s">
         <v>6</v>
@@ -69069,12 +69447,12 @@
         <v>2708</v>
       </c>
       <c r="I38" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2794</v>
+        <v>2746</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -69083,10 +69461,10 @@
         <v>891</v>
       </c>
       <c r="D39" t="s">
-        <v>2819</v>
+        <v>2799</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F39" t="s">
         <v>6</v>
@@ -69098,12 +69476,12 @@
         <v>2708</v>
       </c>
       <c r="I39" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2795</v>
+        <v>2747</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -69112,10 +69490,10 @@
         <v>891</v>
       </c>
       <c r="D40" t="s">
-        <v>2820</v>
+        <v>2800</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F40" t="s">
         <v>6</v>
@@ -69127,12 +69505,12 @@
         <v>2708</v>
       </c>
       <c r="I40" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2796</v>
+        <v>2748</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -69141,10 +69519,10 @@
         <v>891</v>
       </c>
       <c r="D41" t="s">
-        <v>2821</v>
+        <v>2801</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F41" t="s">
         <v>6</v>
@@ -69156,12 +69534,12 @@
         <v>2708</v>
       </c>
       <c r="I41" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2797</v>
+        <v>2749</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -69170,10 +69548,10 @@
         <v>891</v>
       </c>
       <c r="D42" t="s">
-        <v>2822</v>
+        <v>2802</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F42" t="s">
         <v>6</v>
@@ -69185,12 +69563,12 @@
         <v>2708</v>
       </c>
       <c r="I42" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2798</v>
+        <v>2750</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -69199,10 +69577,10 @@
         <v>891</v>
       </c>
       <c r="D43" t="s">
-        <v>2823</v>
+        <v>2803</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F43" t="s">
         <v>6</v>
@@ -69214,12 +69592,12 @@
         <v>2708</v>
       </c>
       <c r="I43" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2799</v>
+        <v>2751</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -69228,10 +69606,10 @@
         <v>891</v>
       </c>
       <c r="D44" t="s">
-        <v>2824</v>
+        <v>2804</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F44" t="s">
         <v>6</v>
@@ -69243,12 +69621,12 @@
         <v>2708</v>
       </c>
       <c r="I44" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2800</v>
+        <v>2752</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -69257,10 +69635,10 @@
         <v>891</v>
       </c>
       <c r="D45" t="s">
-        <v>2825</v>
+        <v>2805</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F45" t="s">
         <v>6</v>
@@ -69272,12 +69650,12 @@
         <v>2708</v>
       </c>
       <c r="I45" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>2801</v>
+        <v>2753</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -69286,10 +69664,10 @@
         <v>891</v>
       </c>
       <c r="D46" t="s">
-        <v>2826</v>
+        <v>2806</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F46" t="s">
         <v>6</v>
@@ -69301,12 +69679,12 @@
         <v>2708</v>
       </c>
       <c r="I46" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>2802</v>
+        <v>2754</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -69315,10 +69693,10 @@
         <v>891</v>
       </c>
       <c r="D47" t="s">
-        <v>2827</v>
+        <v>2807</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F47" t="s">
         <v>6</v>
@@ -69330,12 +69708,12 @@
         <v>2708</v>
       </c>
       <c r="I47" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2803</v>
+        <v>2755</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -69344,10 +69722,10 @@
         <v>891</v>
       </c>
       <c r="D48" t="s">
-        <v>2828</v>
+        <v>2808</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F48" t="s">
         <v>6</v>
@@ -69359,12 +69737,12 @@
         <v>2708</v>
       </c>
       <c r="I48" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>2804</v>
+        <v>2756</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -69373,10 +69751,10 @@
         <v>891</v>
       </c>
       <c r="D49" t="s">
-        <v>2829</v>
+        <v>2809</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F49" t="s">
         <v>6</v>
@@ -69388,24 +69766,24 @@
         <v>2708</v>
       </c>
       <c r="I49" t="s">
-        <v>2805</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2714</v>
+        <v>2836</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
         <v>891</v>
       </c>
       <c r="D50" t="s">
-        <v>2733</v>
+        <v>2876</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F50" t="s">
         <v>6</v>
@@ -69417,24 +69795,24 @@
         <v>2708</v>
       </c>
       <c r="I50" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2707</v>
+        <v>2837</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
         <v>891</v>
       </c>
       <c r="D51" t="s">
-        <v>2734</v>
+        <v>2877</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F51" t="s">
         <v>6</v>
@@ -69446,24 +69824,24 @@
         <v>2708</v>
       </c>
       <c r="I51" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2710</v>
+        <v>2838</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
         <v>891</v>
       </c>
       <c r="D52" t="s">
-        <v>2735</v>
+        <v>2878</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F52" t="s">
         <v>6</v>
@@ -69475,24 +69853,24 @@
         <v>2708</v>
       </c>
       <c r="I52" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2711</v>
+        <v>2839</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
         <v>891</v>
       </c>
       <c r="D53" t="s">
-        <v>2736</v>
+        <v>2879</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F53" t="s">
         <v>6</v>
@@ -69504,24 +69882,24 @@
         <v>2708</v>
       </c>
       <c r="I53" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>2712</v>
+        <v>2840</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
         <v>891</v>
       </c>
       <c r="D54" t="s">
-        <v>2737</v>
+        <v>2880</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F54" t="s">
         <v>6</v>
@@ -69533,24 +69911,24 @@
         <v>2708</v>
       </c>
       <c r="I54" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2713</v>
+        <v>2841</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
         <v>891</v>
       </c>
       <c r="D55" t="s">
-        <v>2738</v>
+        <v>2881</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F55" t="s">
         <v>6</v>
@@ -69562,24 +69940,24 @@
         <v>2708</v>
       </c>
       <c r="I55" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2715</v>
+        <v>2842</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
         <v>891</v>
       </c>
       <c r="D56" t="s">
-        <v>2739</v>
+        <v>2882</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F56" t="s">
         <v>6</v>
@@ -69591,24 +69969,24 @@
         <v>2708</v>
       </c>
       <c r="I56" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2716</v>
+        <v>2843</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
         <v>891</v>
       </c>
       <c r="D57" t="s">
-        <v>2740</v>
+        <v>2883</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -69620,24 +69998,24 @@
         <v>2708</v>
       </c>
       <c r="I57" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2717</v>
+        <v>2844</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="s">
         <v>891</v>
       </c>
       <c r="D58" t="s">
-        <v>2741</v>
+        <v>2884</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
@@ -69649,24 +70027,24 @@
         <v>2708</v>
       </c>
       <c r="I58" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>2718</v>
+        <v>2845</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
         <v>891</v>
       </c>
       <c r="D59" t="s">
-        <v>2742</v>
+        <v>2885</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F59" t="s">
         <v>6</v>
@@ -69678,24 +70056,24 @@
         <v>2708</v>
       </c>
       <c r="I59" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>2719</v>
+        <v>2846</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="s">
         <v>891</v>
       </c>
       <c r="D60" t="s">
-        <v>2743</v>
+        <v>2886</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
@@ -69707,24 +70085,24 @@
         <v>2708</v>
       </c>
       <c r="I60" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>2720</v>
+        <v>2847</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="s">
         <v>891</v>
       </c>
       <c r="D61" t="s">
-        <v>2744</v>
+        <v>2887</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
@@ -69736,24 +70114,24 @@
         <v>2708</v>
       </c>
       <c r="I61" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2721</v>
+        <v>2848</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
         <v>891</v>
       </c>
       <c r="D62" t="s">
-        <v>2745</v>
+        <v>2888</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
@@ -69765,24 +70143,24 @@
         <v>2708</v>
       </c>
       <c r="I62" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2722</v>
+        <v>2849</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="s">
         <v>891</v>
       </c>
       <c r="D63" t="s">
-        <v>2746</v>
+        <v>2889</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F63" t="s">
         <v>6</v>
@@ -69794,24 +70172,24 @@
         <v>2708</v>
       </c>
       <c r="I63" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2723</v>
+        <v>2850</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="s">
         <v>891</v>
       </c>
       <c r="D64" t="s">
-        <v>2747</v>
+        <v>2890</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F64" t="s">
         <v>6</v>
@@ -69823,24 +70201,24 @@
         <v>2708</v>
       </c>
       <c r="I64" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>2724</v>
+        <v>2851</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="s">
         <v>891</v>
       </c>
       <c r="D65" t="s">
-        <v>2748</v>
+        <v>2891</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
@@ -69852,24 +70230,24 @@
         <v>2708</v>
       </c>
       <c r="I65" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2725</v>
+        <v>2852</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="s">
         <v>891</v>
       </c>
       <c r="D66" t="s">
-        <v>2749</v>
+        <v>2892</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -69881,24 +70259,24 @@
         <v>2708</v>
       </c>
       <c r="I66" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>2726</v>
+        <v>2853</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="s">
         <v>891</v>
       </c>
       <c r="D67" t="s">
-        <v>2750</v>
+        <v>2893</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -69910,24 +70288,24 @@
         <v>2708</v>
       </c>
       <c r="I67" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2727</v>
+        <v>2854</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="s">
         <v>891</v>
       </c>
       <c r="D68" t="s">
-        <v>2751</v>
+        <v>2894</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -69939,24 +70317,24 @@
         <v>2708</v>
       </c>
       <c r="I68" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2728</v>
+        <v>2855</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="s">
         <v>891</v>
       </c>
       <c r="D69" t="s">
-        <v>2752</v>
+        <v>2895</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -69968,24 +70346,24 @@
         <v>2708</v>
       </c>
       <c r="I69" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>2729</v>
+        <v>2856</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="s">
         <v>891</v>
       </c>
       <c r="D70" t="s">
-        <v>2753</v>
+        <v>2896</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -69997,24 +70375,24 @@
         <v>2708</v>
       </c>
       <c r="I70" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>2730</v>
+        <v>2866</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="s">
         <v>891</v>
       </c>
       <c r="D71" t="s">
-        <v>2754</v>
+        <v>2897</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -70026,24 +70404,24 @@
         <v>2708</v>
       </c>
       <c r="I71" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>2731</v>
+        <v>2857</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="s">
         <v>891</v>
       </c>
       <c r="D72" t="s">
-        <v>2755</v>
+        <v>2898</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -70055,24 +70433,24 @@
         <v>2708</v>
       </c>
       <c r="I72" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>2732</v>
+        <v>2871</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="s">
         <v>891</v>
       </c>
       <c r="D73" t="s">
-        <v>2756</v>
+        <v>2899</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -70084,24 +70462,24 @@
         <v>2708</v>
       </c>
       <c r="I73" t="s">
-        <v>2709</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>2781</v>
+        <v>2858</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="s">
         <v>891</v>
       </c>
       <c r="D74" t="s">
-        <v>2830</v>
+        <v>2900</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -70113,24 +70491,24 @@
         <v>2708</v>
       </c>
       <c r="I74" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>2782</v>
+        <v>2867</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" t="s">
         <v>891</v>
       </c>
       <c r="D75" t="s">
-        <v>2831</v>
+        <v>2901</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -70142,24 +70520,24 @@
         <v>2708</v>
       </c>
       <c r="I75" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>2783</v>
+        <v>2859</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="s">
         <v>891</v>
       </c>
       <c r="D76" t="s">
-        <v>2832</v>
+        <v>2902</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -70171,24 +70549,24 @@
         <v>2708</v>
       </c>
       <c r="I76" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>2784</v>
+        <v>2872</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="s">
         <v>891</v>
       </c>
       <c r="D77" t="s">
-        <v>2833</v>
+        <v>2903</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -70200,24 +70578,24 @@
         <v>2708</v>
       </c>
       <c r="I77" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>2785</v>
+        <v>2860</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s">
         <v>891</v>
       </c>
       <c r="D78" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>2834</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>2854</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -70229,24 +70607,24 @@
         <v>2708</v>
       </c>
       <c r="I78" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2786</v>
+        <v>2868</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="s">
         <v>891</v>
       </c>
       <c r="D79" t="s">
-        <v>2835</v>
+        <v>2905</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -70258,24 +70636,24 @@
         <v>2708</v>
       </c>
       <c r="I79" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2787</v>
+        <v>2861</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" t="s">
         <v>891</v>
       </c>
       <c r="D80" t="s">
-        <v>2836</v>
+        <v>2906</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -70287,24 +70665,24 @@
         <v>2708</v>
       </c>
       <c r="I80" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>2788</v>
+        <v>2873</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="s">
         <v>891</v>
       </c>
       <c r="D81" t="s">
-        <v>2837</v>
+        <v>2907</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -70316,24 +70694,24 @@
         <v>2708</v>
       </c>
       <c r="I81" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>2789</v>
+        <v>2862</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="s">
         <v>891</v>
       </c>
       <c r="D82" t="s">
-        <v>2838</v>
+        <v>2908</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -70345,24 +70723,24 @@
         <v>2708</v>
       </c>
       <c r="I82" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>2790</v>
+        <v>2869</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" t="s">
         <v>891</v>
       </c>
       <c r="D83" t="s">
-        <v>2839</v>
+        <v>2909</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -70374,24 +70752,24 @@
         <v>2708</v>
       </c>
       <c r="I83" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>2791</v>
+        <v>2863</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="s">
         <v>891</v>
       </c>
       <c r="D84" t="s">
-        <v>2840</v>
+        <v>2910</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -70403,24 +70781,24 @@
         <v>2708</v>
       </c>
       <c r="I84" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>2792</v>
+        <v>2874</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="s">
         <v>891</v>
       </c>
       <c r="D85" t="s">
-        <v>2841</v>
+        <v>2911</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -70432,24 +70810,24 @@
         <v>2708</v>
       </c>
       <c r="I85" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>2793</v>
+        <v>2864</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="s">
         <v>891</v>
       </c>
       <c r="D86" t="s">
-        <v>2842</v>
+        <v>2912</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -70461,24 +70839,24 @@
         <v>2708</v>
       </c>
       <c r="I86" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>2794</v>
+        <v>2870</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="s">
         <v>891</v>
       </c>
       <c r="D87" t="s">
-        <v>2843</v>
+        <v>2913</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -70490,24 +70868,24 @@
         <v>2708</v>
       </c>
       <c r="I87" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>2795</v>
+        <v>2865</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="s">
         <v>891</v>
       </c>
       <c r="D88" t="s">
-        <v>2844</v>
+        <v>2914</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -70519,24 +70897,24 @@
         <v>2708</v>
       </c>
       <c r="I88" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>2796</v>
+        <v>2875</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="s">
         <v>891</v>
       </c>
       <c r="D89" t="s">
-        <v>2845</v>
+        <v>2915</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -70548,24 +70926,24 @@
         <v>2708</v>
       </c>
       <c r="I89" t="s">
-        <v>2805</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>2797</v>
+        <v>2917</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>891</v>
+        <v>557</v>
       </c>
       <c r="D90" t="s">
-        <v>2846</v>
+        <v>2962</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>2854</v>
+        <v>3007</v>
       </c>
       <c r="F90" t="s">
         <v>6</v>
@@ -70577,24 +70955,21 @@
         <v>2708</v>
       </c>
       <c r="I90" t="s">
-        <v>2805</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>2798</v>
+        <v>2918</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="s">
         <v>891</v>
       </c>
       <c r="D91" t="s">
-        <v>2847</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>2854</v>
+        <v>2974</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -70606,24 +70981,21 @@
         <v>2708</v>
       </c>
       <c r="I91" t="s">
-        <v>2805</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>2799</v>
+        <v>2919</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="s">
         <v>891</v>
       </c>
       <c r="D92" t="s">
-        <v>2848</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>2854</v>
+        <v>2963</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -70635,24 +71007,21 @@
         <v>2708</v>
       </c>
       <c r="I92" t="s">
-        <v>2805</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>2800</v>
+        <v>2920</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93" t="s">
         <v>891</v>
       </c>
       <c r="D93" t="s">
-        <v>2849</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>2854</v>
+        <v>2964</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -70664,24 +71033,21 @@
         <v>2708</v>
       </c>
       <c r="I93" t="s">
-        <v>2805</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>2801</v>
+        <v>2921</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" t="s">
         <v>891</v>
       </c>
       <c r="D94" t="s">
-        <v>2850</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>2854</v>
+        <v>2965</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -70693,24 +71059,21 @@
         <v>2708</v>
       </c>
       <c r="I94" t="s">
-        <v>2805</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>2802</v>
+        <v>2922</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" t="s">
         <v>891</v>
       </c>
       <c r="D95" t="s">
-        <v>2851</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>2854</v>
+        <v>2966</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>
@@ -70722,24 +71085,21 @@
         <v>2708</v>
       </c>
       <c r="I95" t="s">
-        <v>2805</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>2803</v>
+        <v>2923</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96" t="s">
         <v>891</v>
       </c>
       <c r="D96" t="s">
-        <v>2852</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>2854</v>
+        <v>2967</v>
       </c>
       <c r="F96" t="s">
         <v>6</v>
@@ -70751,24 +71111,21 @@
         <v>2708</v>
       </c>
       <c r="I96" t="s">
-        <v>2805</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>2804</v>
+        <v>2924</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" t="s">
         <v>891</v>
       </c>
       <c r="D97" t="s">
-        <v>2853</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>2854</v>
+        <v>2968</v>
       </c>
       <c r="F97" t="s">
         <v>6</v>
@@ -70780,7 +71137,4694 @@
         <v>2708</v>
       </c>
       <c r="I97" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>2925</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>891</v>
+      </c>
+      <c r="D98" t="s">
+        <v>2969</v>
+      </c>
+      <c r="F98" t="s">
+        <v>6</v>
+      </c>
+      <c r="G98" t="s">
+        <v>37</v>
+      </c>
+      <c r="H98" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I98" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>891</v>
+      </c>
+      <c r="D99" t="s">
+        <v>2970</v>
+      </c>
+      <c r="F99" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" t="s">
+        <v>37</v>
+      </c>
+      <c r="H99" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I99" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>2927</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>891</v>
+      </c>
+      <c r="D100" t="s">
+        <v>2971</v>
+      </c>
+      <c r="F100" t="s">
+        <v>6</v>
+      </c>
+      <c r="G100" t="s">
+        <v>37</v>
+      </c>
+      <c r="H100" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I100" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>891</v>
+      </c>
+      <c r="D101" t="s">
+        <v>2972</v>
+      </c>
+      <c r="F101" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" t="s">
+        <v>37</v>
+      </c>
+      <c r="H101" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I101" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>2929</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>891</v>
+      </c>
+      <c r="D102" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F102" t="s">
+        <v>6</v>
+      </c>
+      <c r="G102" t="s">
+        <v>37</v>
+      </c>
+      <c r="H102" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I102" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>891</v>
+      </c>
+      <c r="D103" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F103" t="s">
+        <v>6</v>
+      </c>
+      <c r="G103" t="s">
+        <v>37</v>
+      </c>
+      <c r="H103" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I103" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>891</v>
+      </c>
+      <c r="D104" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F104" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" t="s">
+        <v>37</v>
+      </c>
+      <c r="H104" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I104" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>891</v>
+      </c>
+      <c r="D105" t="s">
+        <v>2977</v>
+      </c>
+      <c r="F105" t="s">
+        <v>6</v>
+      </c>
+      <c r="G105" t="s">
+        <v>37</v>
+      </c>
+      <c r="H105" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I105" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>891</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>2987</v>
+      </c>
+      <c r="F106" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" t="s">
+        <v>37</v>
+      </c>
+      <c r="H106" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I106" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107" t="s">
+        <v>891</v>
+      </c>
+      <c r="D107" t="s">
+        <v>2978</v>
+      </c>
+      <c r="F107" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" t="s">
+        <v>37</v>
+      </c>
+      <c r="H107" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I107" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>891</v>
+      </c>
+      <c r="D108" t="s">
+        <v>2979</v>
+      </c>
+      <c r="F108" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" t="s">
+        <v>37</v>
+      </c>
+      <c r="H108" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I108" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>891</v>
+      </c>
+      <c r="D109" t="s">
+        <v>2980</v>
+      </c>
+      <c r="F109" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" t="s">
+        <v>37</v>
+      </c>
+      <c r="H109" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I109" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>891</v>
+      </c>
+      <c r="D110" t="s">
+        <v>2981</v>
+      </c>
+      <c r="F110" t="s">
+        <v>6</v>
+      </c>
+      <c r="G110" t="s">
+        <v>37</v>
+      </c>
+      <c r="H110" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I110" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>891</v>
+      </c>
+      <c r="D111" t="s">
+        <v>2982</v>
+      </c>
+      <c r="F111" t="s">
+        <v>6</v>
+      </c>
+      <c r="G111" t="s">
+        <v>37</v>
+      </c>
+      <c r="H111" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I111" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>891</v>
+      </c>
+      <c r="D112" t="s">
+        <v>2983</v>
+      </c>
+      <c r="F112" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" t="s">
+        <v>37</v>
+      </c>
+      <c r="H112" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I112" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>891</v>
+      </c>
+      <c r="D113" t="s">
+        <v>2984</v>
+      </c>
+      <c r="F113" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" t="s">
+        <v>37</v>
+      </c>
+      <c r="H113" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I113" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>891</v>
+      </c>
+      <c r="D114" t="s">
+        <v>2985</v>
+      </c>
+      <c r="F114" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" t="s">
+        <v>37</v>
+      </c>
+      <c r="H114" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I114" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
+        <v>891</v>
+      </c>
+      <c r="D115" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F115" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" t="s">
+        <v>37</v>
+      </c>
+      <c r="H115" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I115" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
+        <v>891</v>
+      </c>
+      <c r="D116" t="s">
+        <v>2988</v>
+      </c>
+      <c r="F116" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" t="s">
+        <v>37</v>
+      </c>
+      <c r="H116" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I116" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117" t="s">
+        <v>891</v>
+      </c>
+      <c r="D117" t="s">
+        <v>2989</v>
+      </c>
+      <c r="F117" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" t="s">
+        <v>37</v>
+      </c>
+      <c r="H117" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I117" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>2945</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>891</v>
+      </c>
+      <c r="D118" t="s">
+        <v>2990</v>
+      </c>
+      <c r="F118" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" t="s">
+        <v>37</v>
+      </c>
+      <c r="H118" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I118" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
+        <v>891</v>
+      </c>
+      <c r="D119" t="s">
+        <v>2991</v>
+      </c>
+      <c r="F119" t="s">
+        <v>6</v>
+      </c>
+      <c r="G119" t="s">
+        <v>37</v>
+      </c>
+      <c r="H119" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I119" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120" t="s">
+        <v>891</v>
+      </c>
+      <c r="D120" t="s">
+        <v>2992</v>
+      </c>
+      <c r="F120" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" t="s">
+        <v>37</v>
+      </c>
+      <c r="H120" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I120" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121" t="s">
+        <v>891</v>
+      </c>
+      <c r="D121" t="s">
+        <v>2994</v>
+      </c>
+      <c r="F121" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" t="s">
+        <v>37</v>
+      </c>
+      <c r="H121" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I121" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>891</v>
+      </c>
+      <c r="D122" t="s">
+        <v>2993</v>
+      </c>
+      <c r="F122" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" t="s">
+        <v>37</v>
+      </c>
+      <c r="H122" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I122" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>891</v>
+      </c>
+      <c r="D123" t="s">
+        <v>2995</v>
+      </c>
+      <c r="F123" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" t="s">
+        <v>37</v>
+      </c>
+      <c r="H123" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I123" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
+        <v>891</v>
+      </c>
+      <c r="D124" t="s">
+        <v>2996</v>
+      </c>
+      <c r="F124" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" t="s">
+        <v>37</v>
+      </c>
+      <c r="H124" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I124" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125" t="s">
+        <v>891</v>
+      </c>
+      <c r="D125" t="s">
+        <v>2997</v>
+      </c>
+      <c r="F125" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" t="s">
+        <v>37</v>
+      </c>
+      <c r="H125" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I125" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126" t="s">
+        <v>891</v>
+      </c>
+      <c r="D126" t="s">
+        <v>2998</v>
+      </c>
+      <c r="F126" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" t="s">
+        <v>37</v>
+      </c>
+      <c r="H126" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I126" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>2954</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>891</v>
+      </c>
+      <c r="D127" t="s">
+        <v>3003</v>
+      </c>
+      <c r="F127" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" t="s">
+        <v>37</v>
+      </c>
+      <c r="H127" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I127" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>2955</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128" t="s">
+        <v>891</v>
+      </c>
+      <c r="D128" t="s">
+        <v>2999</v>
+      </c>
+      <c r="F128" t="s">
+        <v>6</v>
+      </c>
+      <c r="G128" t="s">
+        <v>37</v>
+      </c>
+      <c r="H128" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I128" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>2956</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129" t="s">
+        <v>891</v>
+      </c>
+      <c r="D129" t="s">
+        <v>3000</v>
+      </c>
+      <c r="F129" t="s">
+        <v>6</v>
+      </c>
+      <c r="G129" t="s">
+        <v>37</v>
+      </c>
+      <c r="H129" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I129" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
+        <v>891</v>
+      </c>
+      <c r="D130" t="s">
+        <v>3004</v>
+      </c>
+      <c r="F130" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" t="s">
+        <v>37</v>
+      </c>
+      <c r="H130" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I130" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131" t="s">
+        <v>891</v>
+      </c>
+      <c r="D131" t="s">
+        <v>3001</v>
+      </c>
+      <c r="F131" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" t="s">
+        <v>37</v>
+      </c>
+      <c r="H131" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I131" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>2959</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132" t="s">
+        <v>891</v>
+      </c>
+      <c r="D132" t="s">
+        <v>3002</v>
+      </c>
+      <c r="F132" t="s">
+        <v>6</v>
+      </c>
+      <c r="G132" t="s">
+        <v>37</v>
+      </c>
+      <c r="H132" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I132" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133" t="s">
+        <v>891</v>
+      </c>
+      <c r="D133" t="s">
+        <v>3005</v>
+      </c>
+      <c r="F133" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" t="s">
+        <v>37</v>
+      </c>
+      <c r="H133" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I133" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>891</v>
+      </c>
+      <c r="D134" t="s">
+        <v>3006</v>
+      </c>
+      <c r="F134" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" t="s">
+        <v>37</v>
+      </c>
+      <c r="H134" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I134" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>891</v>
+      </c>
+      <c r="D135" t="s">
+        <v>2810</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F135" t="s">
+        <v>6</v>
+      </c>
+      <c r="G135" t="s">
+        <v>37</v>
+      </c>
+      <c r="H135" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I135" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+      <c r="C136" t="s">
+        <v>891</v>
+      </c>
+      <c r="D136" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F136" t="s">
+        <v>6</v>
+      </c>
+      <c r="G136" t="s">
+        <v>37</v>
+      </c>
+      <c r="H136" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I136" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137" t="s">
+        <v>891</v>
+      </c>
+      <c r="D137" t="s">
+        <v>2812</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F137" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" t="s">
+        <v>37</v>
+      </c>
+      <c r="H137" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I137" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>2711</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
+        <v>891</v>
+      </c>
+      <c r="D138" t="s">
+        <v>2813</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F138" t="s">
+        <v>6</v>
+      </c>
+      <c r="G138" t="s">
+        <v>37</v>
+      </c>
+      <c r="H138" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I138" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>891</v>
+      </c>
+      <c r="D139" t="s">
+        <v>2814</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F139" t="s">
+        <v>6</v>
+      </c>
+      <c r="G139" t="s">
+        <v>37</v>
+      </c>
+      <c r="H139" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I139" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>891</v>
+      </c>
+      <c r="D140" t="s">
+        <v>2815</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F140" t="s">
+        <v>6</v>
+      </c>
+      <c r="G140" t="s">
+        <v>37</v>
+      </c>
+      <c r="H140" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I140" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141" t="s">
+        <v>891</v>
+      </c>
+      <c r="D141" t="s">
+        <v>2816</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F141" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" t="s">
+        <v>37</v>
+      </c>
+      <c r="H141" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I141" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
+      </c>
+      <c r="C142" t="s">
+        <v>891</v>
+      </c>
+      <c r="D142" t="s">
+        <v>2817</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F142" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" t="s">
+        <v>37</v>
+      </c>
+      <c r="H142" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I142" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>891</v>
+      </c>
+      <c r="D143" t="s">
+        <v>2818</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F143" t="s">
+        <v>6</v>
+      </c>
+      <c r="G143" t="s">
+        <v>37</v>
+      </c>
+      <c r="H143" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I143" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>891</v>
+      </c>
+      <c r="D144" t="s">
+        <v>2819</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F144" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" t="s">
+        <v>37</v>
+      </c>
+      <c r="H144" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I144" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B145">
+        <v>2</v>
+      </c>
+      <c r="C145" t="s">
+        <v>891</v>
+      </c>
+      <c r="D145" t="s">
+        <v>2820</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F145" t="s">
+        <v>6</v>
+      </c>
+      <c r="G145" t="s">
+        <v>37</v>
+      </c>
+      <c r="H145" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I145" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146" t="s">
+        <v>891</v>
+      </c>
+      <c r="D146" t="s">
+        <v>2821</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F146" t="s">
+        <v>6</v>
+      </c>
+      <c r="G146" t="s">
+        <v>37</v>
+      </c>
+      <c r="H146" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I146" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>891</v>
+      </c>
+      <c r="D147" t="s">
+        <v>2822</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F147" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" t="s">
+        <v>37</v>
+      </c>
+      <c r="H147" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I147" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>891</v>
+      </c>
+      <c r="D148" t="s">
+        <v>2823</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F148" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" t="s">
+        <v>37</v>
+      </c>
+      <c r="H148" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I148" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>2723</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>891</v>
+      </c>
+      <c r="D149" t="s">
+        <v>2824</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F149" t="s">
+        <v>6</v>
+      </c>
+      <c r="G149" t="s">
+        <v>37</v>
+      </c>
+      <c r="H149" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I149" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>891</v>
+      </c>
+      <c r="D150" t="s">
+        <v>2825</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F150" t="s">
+        <v>6</v>
+      </c>
+      <c r="G150" t="s">
+        <v>37</v>
+      </c>
+      <c r="H150" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I150" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>891</v>
+      </c>
+      <c r="D151" t="s">
+        <v>2826</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F151" t="s">
+        <v>6</v>
+      </c>
+      <c r="G151" t="s">
+        <v>37</v>
+      </c>
+      <c r="H151" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I151" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>891</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2827</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F152" t="s">
+        <v>6</v>
+      </c>
+      <c r="G152" t="s">
+        <v>37</v>
+      </c>
+      <c r="H152" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I152" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>2727</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>891</v>
+      </c>
+      <c r="D153" t="s">
+        <v>2828</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F153" t="s">
+        <v>6</v>
+      </c>
+      <c r="G153" t="s">
+        <v>37</v>
+      </c>
+      <c r="H153" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I153" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>2728</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154" t="s">
+        <v>891</v>
+      </c>
+      <c r="D154" t="s">
+        <v>2829</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F154" t="s">
+        <v>6</v>
+      </c>
+      <c r="G154" t="s">
+        <v>37</v>
+      </c>
+      <c r="H154" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I154" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>2729</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>891</v>
+      </c>
+      <c r="D155" t="s">
+        <v>2830</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F155" t="s">
+        <v>6</v>
+      </c>
+      <c r="G155" t="s">
+        <v>37</v>
+      </c>
+      <c r="H155" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I155" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156" t="s">
+        <v>891</v>
+      </c>
+      <c r="D156" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F156" t="s">
+        <v>6</v>
+      </c>
+      <c r="G156" t="s">
+        <v>37</v>
+      </c>
+      <c r="H156" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I156" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>2731</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157" t="s">
+        <v>891</v>
+      </c>
+      <c r="D157" t="s">
+        <v>2832</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F157" t="s">
+        <v>6</v>
+      </c>
+      <c r="G157" t="s">
+        <v>37</v>
+      </c>
+      <c r="H157" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I157" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="C158" t="s">
+        <v>891</v>
+      </c>
+      <c r="D158" t="s">
+        <v>2833</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F158" t="s">
+        <v>6</v>
+      </c>
+      <c r="G158" t="s">
+        <v>37</v>
+      </c>
+      <c r="H158" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I158" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>2733</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>891</v>
+      </c>
+      <c r="D159" t="s">
+        <v>2786</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F159" t="s">
+        <v>6</v>
+      </c>
+      <c r="G159" t="s">
+        <v>37</v>
+      </c>
+      <c r="H159" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I159" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="C160" t="s">
+        <v>891</v>
+      </c>
+      <c r="D160" t="s">
+        <v>2787</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F160" t="s">
+        <v>6</v>
+      </c>
+      <c r="G160" t="s">
+        <v>37</v>
+      </c>
+      <c r="H160" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I160" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+      <c r="C161" t="s">
+        <v>891</v>
+      </c>
+      <c r="D161" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F161" t="s">
+        <v>6</v>
+      </c>
+      <c r="G161" t="s">
+        <v>37</v>
+      </c>
+      <c r="H161" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I161" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B162">
+        <v>2</v>
+      </c>
+      <c r="C162" t="s">
+        <v>891</v>
+      </c>
+      <c r="D162" t="s">
+        <v>2789</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F162" t="s">
+        <v>6</v>
+      </c>
+      <c r="G162" t="s">
+        <v>37</v>
+      </c>
+      <c r="H162" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I162" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>2737</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163" t="s">
+        <v>891</v>
+      </c>
+      <c r="D163" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F163" t="s">
+        <v>6</v>
+      </c>
+      <c r="G163" t="s">
+        <v>37</v>
+      </c>
+      <c r="H163" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I163" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164" t="s">
+        <v>891</v>
+      </c>
+      <c r="D164" t="s">
+        <v>2791</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F164" t="s">
+        <v>6</v>
+      </c>
+      <c r="G164" t="s">
+        <v>37</v>
+      </c>
+      <c r="H164" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I164" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>2739</v>
+      </c>
+      <c r="B165">
+        <v>2</v>
+      </c>
+      <c r="C165" t="s">
+        <v>891</v>
+      </c>
+      <c r="D165" t="s">
+        <v>2792</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F165" t="s">
+        <v>6</v>
+      </c>
+      <c r="G165" t="s">
+        <v>37</v>
+      </c>
+      <c r="H165" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I165" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+      <c r="C166" t="s">
+        <v>891</v>
+      </c>
+      <c r="D166" t="s">
+        <v>2793</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F166" t="s">
+        <v>6</v>
+      </c>
+      <c r="G166" t="s">
+        <v>37</v>
+      </c>
+      <c r="H166" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I166" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167" t="s">
+        <v>891</v>
+      </c>
+      <c r="D167" t="s">
+        <v>2794</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F167" t="s">
+        <v>6</v>
+      </c>
+      <c r="G167" t="s">
+        <v>37</v>
+      </c>
+      <c r="H167" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I167" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B168">
+        <v>2</v>
+      </c>
+      <c r="C168" t="s">
+        <v>891</v>
+      </c>
+      <c r="D168" t="s">
+        <v>2795</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F168" t="s">
+        <v>6</v>
+      </c>
+      <c r="G168" t="s">
+        <v>37</v>
+      </c>
+      <c r="H168" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I168" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>2743</v>
+      </c>
+      <c r="B169">
+        <v>2</v>
+      </c>
+      <c r="C169" t="s">
+        <v>891</v>
+      </c>
+      <c r="D169" t="s">
+        <v>2796</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F169" t="s">
+        <v>6</v>
+      </c>
+      <c r="G169" t="s">
+        <v>37</v>
+      </c>
+      <c r="H169" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I169" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B170">
+        <v>2</v>
+      </c>
+      <c r="C170" t="s">
+        <v>891</v>
+      </c>
+      <c r="D170" t="s">
+        <v>2797</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F170" t="s">
+        <v>6</v>
+      </c>
+      <c r="G170" t="s">
+        <v>37</v>
+      </c>
+      <c r="H170" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I170" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>2745</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171" t="s">
+        <v>891</v>
+      </c>
+      <c r="D171" t="s">
+        <v>2798</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F171" t="s">
+        <v>6</v>
+      </c>
+      <c r="G171" t="s">
+        <v>37</v>
+      </c>
+      <c r="H171" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I171" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B172">
+        <v>2</v>
+      </c>
+      <c r="C172" t="s">
+        <v>891</v>
+      </c>
+      <c r="D172" t="s">
+        <v>2799</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F172" t="s">
+        <v>6</v>
+      </c>
+      <c r="G172" t="s">
+        <v>37</v>
+      </c>
+      <c r="H172" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I172" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>2747</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
+      <c r="C173" t="s">
+        <v>891</v>
+      </c>
+      <c r="D173" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F173" t="s">
+        <v>6</v>
+      </c>
+      <c r="G173" t="s">
+        <v>37</v>
+      </c>
+      <c r="H173" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I173" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B174">
+        <v>2</v>
+      </c>
+      <c r="C174" t="s">
+        <v>891</v>
+      </c>
+      <c r="D174" t="s">
+        <v>2801</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F174" t="s">
+        <v>6</v>
+      </c>
+      <c r="G174" t="s">
+        <v>37</v>
+      </c>
+      <c r="H174" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I174" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>2749</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+      <c r="C175" t="s">
+        <v>891</v>
+      </c>
+      <c r="D175" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F175" t="s">
+        <v>6</v>
+      </c>
+      <c r="G175" t="s">
+        <v>37</v>
+      </c>
+      <c r="H175" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I175" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B176">
+        <v>2</v>
+      </c>
+      <c r="C176" t="s">
+        <v>891</v>
+      </c>
+      <c r="D176" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F176" t="s">
+        <v>6</v>
+      </c>
+      <c r="G176" t="s">
+        <v>37</v>
+      </c>
+      <c r="H176" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I176" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
+      </c>
+      <c r="C177" t="s">
+        <v>891</v>
+      </c>
+      <c r="D177" t="s">
+        <v>2804</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F177" t="s">
+        <v>6</v>
+      </c>
+      <c r="G177" t="s">
+        <v>37</v>
+      </c>
+      <c r="H177" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I177" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B178">
+        <v>2</v>
+      </c>
+      <c r="C178" t="s">
+        <v>891</v>
+      </c>
+      <c r="D178" t="s">
         <v>2805</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F178" t="s">
+        <v>6</v>
+      </c>
+      <c r="G178" t="s">
+        <v>37</v>
+      </c>
+      <c r="H178" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I178" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B179">
+        <v>2</v>
+      </c>
+      <c r="C179" t="s">
+        <v>891</v>
+      </c>
+      <c r="D179" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F179" t="s">
+        <v>6</v>
+      </c>
+      <c r="G179" t="s">
+        <v>37</v>
+      </c>
+      <c r="H179" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I179" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>2754</v>
+      </c>
+      <c r="B180">
+        <v>2</v>
+      </c>
+      <c r="C180" t="s">
+        <v>891</v>
+      </c>
+      <c r="D180" t="s">
+        <v>2807</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F180" t="s">
+        <v>6</v>
+      </c>
+      <c r="G180" t="s">
+        <v>37</v>
+      </c>
+      <c r="H180" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I180" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
+      </c>
+      <c r="C181" t="s">
+        <v>891</v>
+      </c>
+      <c r="D181" t="s">
+        <v>2808</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F181" t="s">
+        <v>6</v>
+      </c>
+      <c r="G181" t="s">
+        <v>37</v>
+      </c>
+      <c r="H181" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I181" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>2756</v>
+      </c>
+      <c r="B182">
+        <v>2</v>
+      </c>
+      <c r="C182" t="s">
+        <v>891</v>
+      </c>
+      <c r="D182" t="s">
+        <v>2809</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F182" t="s">
+        <v>6</v>
+      </c>
+      <c r="G182" t="s">
+        <v>37</v>
+      </c>
+      <c r="H182" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I182" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>2836</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183" t="s">
+        <v>891</v>
+      </c>
+      <c r="D183" t="s">
+        <v>2876</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F183" t="s">
+        <v>6</v>
+      </c>
+      <c r="G183" t="s">
+        <v>37</v>
+      </c>
+      <c r="H183" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I183" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184" t="s">
+        <v>891</v>
+      </c>
+      <c r="D184" t="s">
+        <v>2877</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F184" t="s">
+        <v>6</v>
+      </c>
+      <c r="G184" t="s">
+        <v>37</v>
+      </c>
+      <c r="H184" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I184" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>2838</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+      <c r="C185" t="s">
+        <v>891</v>
+      </c>
+      <c r="D185" t="s">
+        <v>2878</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F185" t="s">
+        <v>6</v>
+      </c>
+      <c r="G185" t="s">
+        <v>37</v>
+      </c>
+      <c r="H185" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I185" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+      <c r="C186" t="s">
+        <v>891</v>
+      </c>
+      <c r="D186" t="s">
+        <v>2879</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F186" t="s">
+        <v>6</v>
+      </c>
+      <c r="G186" t="s">
+        <v>37</v>
+      </c>
+      <c r="H186" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I186" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>2840</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187" t="s">
+        <v>891</v>
+      </c>
+      <c r="D187" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F187" t="s">
+        <v>6</v>
+      </c>
+      <c r="G187" t="s">
+        <v>37</v>
+      </c>
+      <c r="H187" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I187" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>2841</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188" t="s">
+        <v>891</v>
+      </c>
+      <c r="D188" t="s">
+        <v>2881</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F188" t="s">
+        <v>6</v>
+      </c>
+      <c r="G188" t="s">
+        <v>37</v>
+      </c>
+      <c r="H188" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I188" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>2842</v>
+      </c>
+      <c r="B189">
+        <v>2</v>
+      </c>
+      <c r="C189" t="s">
+        <v>891</v>
+      </c>
+      <c r="D189" t="s">
+        <v>2882</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F189" t="s">
+        <v>6</v>
+      </c>
+      <c r="G189" t="s">
+        <v>37</v>
+      </c>
+      <c r="H189" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I189" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B190">
+        <v>2</v>
+      </c>
+      <c r="C190" t="s">
+        <v>891</v>
+      </c>
+      <c r="D190" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F190" t="s">
+        <v>6</v>
+      </c>
+      <c r="G190" t="s">
+        <v>37</v>
+      </c>
+      <c r="H190" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I190" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B191">
+        <v>2</v>
+      </c>
+      <c r="C191" t="s">
+        <v>891</v>
+      </c>
+      <c r="D191" t="s">
+        <v>2884</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F191" t="s">
+        <v>6</v>
+      </c>
+      <c r="G191" t="s">
+        <v>37</v>
+      </c>
+      <c r="H191" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I191" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+      <c r="C192" t="s">
+        <v>891</v>
+      </c>
+      <c r="D192" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F192" t="s">
+        <v>6</v>
+      </c>
+      <c r="G192" t="s">
+        <v>37</v>
+      </c>
+      <c r="H192" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I192" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B193">
+        <v>2</v>
+      </c>
+      <c r="C193" t="s">
+        <v>891</v>
+      </c>
+      <c r="D193" t="s">
+        <v>2886</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F193" t="s">
+        <v>6</v>
+      </c>
+      <c r="G193" t="s">
+        <v>37</v>
+      </c>
+      <c r="H193" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I193" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B194">
+        <v>2</v>
+      </c>
+      <c r="C194" t="s">
+        <v>891</v>
+      </c>
+      <c r="D194" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F194" t="s">
+        <v>6</v>
+      </c>
+      <c r="G194" t="s">
+        <v>37</v>
+      </c>
+      <c r="H194" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I194" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+      <c r="C195" t="s">
+        <v>891</v>
+      </c>
+      <c r="D195" t="s">
+        <v>2888</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F195" t="s">
+        <v>6</v>
+      </c>
+      <c r="G195" t="s">
+        <v>37</v>
+      </c>
+      <c r="H195" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I195" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196" t="s">
+        <v>891</v>
+      </c>
+      <c r="D196" t="s">
+        <v>2889</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F196" t="s">
+        <v>6</v>
+      </c>
+      <c r="G196" t="s">
+        <v>37</v>
+      </c>
+      <c r="H196" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I196" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>2850</v>
+      </c>
+      <c r="B197">
+        <v>2</v>
+      </c>
+      <c r="C197" t="s">
+        <v>891</v>
+      </c>
+      <c r="D197" t="s">
+        <v>2890</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F197" t="s">
+        <v>6</v>
+      </c>
+      <c r="G197" t="s">
+        <v>37</v>
+      </c>
+      <c r="H197" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I197" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B198">
+        <v>2</v>
+      </c>
+      <c r="C198" t="s">
+        <v>891</v>
+      </c>
+      <c r="D198" t="s">
+        <v>2891</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F198" t="s">
+        <v>6</v>
+      </c>
+      <c r="G198" t="s">
+        <v>37</v>
+      </c>
+      <c r="H198" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I198" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B199">
+        <v>2</v>
+      </c>
+      <c r="C199" t="s">
+        <v>891</v>
+      </c>
+      <c r="D199" t="s">
+        <v>2892</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F199" t="s">
+        <v>6</v>
+      </c>
+      <c r="G199" t="s">
+        <v>37</v>
+      </c>
+      <c r="H199" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I199" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>2853</v>
+      </c>
+      <c r="B200">
+        <v>2</v>
+      </c>
+      <c r="C200" t="s">
+        <v>891</v>
+      </c>
+      <c r="D200" t="s">
+        <v>2893</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F200" t="s">
+        <v>6</v>
+      </c>
+      <c r="G200" t="s">
+        <v>37</v>
+      </c>
+      <c r="H200" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I200" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B201">
+        <v>2</v>
+      </c>
+      <c r="C201" t="s">
+        <v>891</v>
+      </c>
+      <c r="D201" t="s">
+        <v>2894</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F201" t="s">
+        <v>6</v>
+      </c>
+      <c r="G201" t="s">
+        <v>37</v>
+      </c>
+      <c r="H201" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I201" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B202">
+        <v>2</v>
+      </c>
+      <c r="C202" t="s">
+        <v>891</v>
+      </c>
+      <c r="D202" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F202" t="s">
+        <v>6</v>
+      </c>
+      <c r="G202" t="s">
+        <v>37</v>
+      </c>
+      <c r="H202" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I202" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B203">
+        <v>2</v>
+      </c>
+      <c r="C203" t="s">
+        <v>891</v>
+      </c>
+      <c r="D203" t="s">
+        <v>2896</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F203" t="s">
+        <v>6</v>
+      </c>
+      <c r="G203" t="s">
+        <v>37</v>
+      </c>
+      <c r="H203" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I203" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B204">
+        <v>2</v>
+      </c>
+      <c r="C204" t="s">
+        <v>891</v>
+      </c>
+      <c r="D204" t="s">
+        <v>2897</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F204" t="s">
+        <v>6</v>
+      </c>
+      <c r="G204" t="s">
+        <v>37</v>
+      </c>
+      <c r="H204" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I204" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B205">
+        <v>2</v>
+      </c>
+      <c r="C205" t="s">
+        <v>891</v>
+      </c>
+      <c r="D205" t="s">
+        <v>2898</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F205" t="s">
+        <v>6</v>
+      </c>
+      <c r="G205" t="s">
+        <v>37</v>
+      </c>
+      <c r="H205" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I205" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B206">
+        <v>2</v>
+      </c>
+      <c r="C206" t="s">
+        <v>891</v>
+      </c>
+      <c r="D206" t="s">
+        <v>2899</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F206" t="s">
+        <v>6</v>
+      </c>
+      <c r="G206" t="s">
+        <v>37</v>
+      </c>
+      <c r="H206" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I206" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B207">
+        <v>2</v>
+      </c>
+      <c r="C207" t="s">
+        <v>891</v>
+      </c>
+      <c r="D207" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F207" t="s">
+        <v>6</v>
+      </c>
+      <c r="G207" t="s">
+        <v>37</v>
+      </c>
+      <c r="H207" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I207" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B208">
+        <v>2</v>
+      </c>
+      <c r="C208" t="s">
+        <v>891</v>
+      </c>
+      <c r="D208" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F208" t="s">
+        <v>6</v>
+      </c>
+      <c r="G208" t="s">
+        <v>37</v>
+      </c>
+      <c r="H208" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I208" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B209">
+        <v>2</v>
+      </c>
+      <c r="C209" t="s">
+        <v>891</v>
+      </c>
+      <c r="D209" t="s">
+        <v>2902</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F209" t="s">
+        <v>6</v>
+      </c>
+      <c r="G209" t="s">
+        <v>37</v>
+      </c>
+      <c r="H209" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I209" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>2872</v>
+      </c>
+      <c r="B210">
+        <v>2</v>
+      </c>
+      <c r="C210" t="s">
+        <v>891</v>
+      </c>
+      <c r="D210" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F210" t="s">
+        <v>6</v>
+      </c>
+      <c r="G210" t="s">
+        <v>37</v>
+      </c>
+      <c r="H210" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I210" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B211">
+        <v>2</v>
+      </c>
+      <c r="C211" t="s">
+        <v>891</v>
+      </c>
+      <c r="D211" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F211" t="s">
+        <v>6</v>
+      </c>
+      <c r="G211" t="s">
+        <v>37</v>
+      </c>
+      <c r="H211" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I211" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B212">
+        <v>2</v>
+      </c>
+      <c r="C212" t="s">
+        <v>891</v>
+      </c>
+      <c r="D212" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F212" t="s">
+        <v>6</v>
+      </c>
+      <c r="G212" t="s">
+        <v>37</v>
+      </c>
+      <c r="H212" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I212" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>2861</v>
+      </c>
+      <c r="B213">
+        <v>2</v>
+      </c>
+      <c r="C213" t="s">
+        <v>891</v>
+      </c>
+      <c r="D213" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F213" t="s">
+        <v>6</v>
+      </c>
+      <c r="G213" t="s">
+        <v>37</v>
+      </c>
+      <c r="H213" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I213" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B214">
+        <v>2</v>
+      </c>
+      <c r="C214" t="s">
+        <v>891</v>
+      </c>
+      <c r="D214" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F214" t="s">
+        <v>6</v>
+      </c>
+      <c r="G214" t="s">
+        <v>37</v>
+      </c>
+      <c r="H214" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I214" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>2862</v>
+      </c>
+      <c r="B215">
+        <v>2</v>
+      </c>
+      <c r="C215" t="s">
+        <v>891</v>
+      </c>
+      <c r="D215" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F215" t="s">
+        <v>6</v>
+      </c>
+      <c r="G215" t="s">
+        <v>37</v>
+      </c>
+      <c r="H215" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I215" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>2869</v>
+      </c>
+      <c r="B216">
+        <v>2</v>
+      </c>
+      <c r="C216" t="s">
+        <v>891</v>
+      </c>
+      <c r="D216" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F216" t="s">
+        <v>6</v>
+      </c>
+      <c r="G216" t="s">
+        <v>37</v>
+      </c>
+      <c r="H216" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I216" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B217">
+        <v>2</v>
+      </c>
+      <c r="C217" t="s">
+        <v>891</v>
+      </c>
+      <c r="D217" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F217" t="s">
+        <v>6</v>
+      </c>
+      <c r="G217" t="s">
+        <v>37</v>
+      </c>
+      <c r="H217" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I217" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B218">
+        <v>2</v>
+      </c>
+      <c r="C218" t="s">
+        <v>891</v>
+      </c>
+      <c r="D218" t="s">
+        <v>2911</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F218" t="s">
+        <v>6</v>
+      </c>
+      <c r="G218" t="s">
+        <v>37</v>
+      </c>
+      <c r="H218" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I218" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B219">
+        <v>2</v>
+      </c>
+      <c r="C219" t="s">
+        <v>891</v>
+      </c>
+      <c r="D219" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F219" t="s">
+        <v>6</v>
+      </c>
+      <c r="G219" t="s">
+        <v>37</v>
+      </c>
+      <c r="H219" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I219" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B220">
+        <v>2</v>
+      </c>
+      <c r="C220" t="s">
+        <v>891</v>
+      </c>
+      <c r="D220" t="s">
+        <v>2913</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F220" t="s">
+        <v>6</v>
+      </c>
+      <c r="G220" t="s">
+        <v>37</v>
+      </c>
+      <c r="H220" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I220" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>2865</v>
+      </c>
+      <c r="B221">
+        <v>2</v>
+      </c>
+      <c r="C221" t="s">
+        <v>891</v>
+      </c>
+      <c r="D221" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F221" t="s">
+        <v>6</v>
+      </c>
+      <c r="G221" t="s">
+        <v>37</v>
+      </c>
+      <c r="H221" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I221" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B222">
+        <v>2</v>
+      </c>
+      <c r="C222" t="s">
+        <v>891</v>
+      </c>
+      <c r="D222" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F222" t="s">
+        <v>6</v>
+      </c>
+      <c r="G222" t="s">
+        <v>37</v>
+      </c>
+      <c r="H222" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I222" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B223">
+        <v>2</v>
+      </c>
+      <c r="C223" t="s">
+        <v>557</v>
+      </c>
+      <c r="D223" t="s">
+        <v>2962</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>3007</v>
+      </c>
+      <c r="F223" t="s">
+        <v>6</v>
+      </c>
+      <c r="G223" t="s">
+        <v>37</v>
+      </c>
+      <c r="H223" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I223" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B224">
+        <v>2</v>
+      </c>
+      <c r="C224" t="s">
+        <v>891</v>
+      </c>
+      <c r="D224" t="s">
+        <v>2974</v>
+      </c>
+      <c r="F224" t="s">
+        <v>6</v>
+      </c>
+      <c r="G224" t="s">
+        <v>37</v>
+      </c>
+      <c r="H224" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I224" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B225">
+        <v>2</v>
+      </c>
+      <c r="C225" t="s">
+        <v>891</v>
+      </c>
+      <c r="D225" t="s">
+        <v>2963</v>
+      </c>
+      <c r="F225" t="s">
+        <v>6</v>
+      </c>
+      <c r="G225" t="s">
+        <v>37</v>
+      </c>
+      <c r="H225" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I225" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B226">
+        <v>2</v>
+      </c>
+      <c r="C226" t="s">
+        <v>891</v>
+      </c>
+      <c r="D226" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F226" t="s">
+        <v>6</v>
+      </c>
+      <c r="G226" t="s">
+        <v>37</v>
+      </c>
+      <c r="H226" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I226" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B227">
+        <v>2</v>
+      </c>
+      <c r="C227" t="s">
+        <v>891</v>
+      </c>
+      <c r="D227" t="s">
+        <v>2965</v>
+      </c>
+      <c r="F227" t="s">
+        <v>6</v>
+      </c>
+      <c r="G227" t="s">
+        <v>37</v>
+      </c>
+      <c r="H227" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I227" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B228">
+        <v>2</v>
+      </c>
+      <c r="C228" t="s">
+        <v>891</v>
+      </c>
+      <c r="D228" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F228" t="s">
+        <v>6</v>
+      </c>
+      <c r="G228" t="s">
+        <v>37</v>
+      </c>
+      <c r="H228" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I228" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>2923</v>
+      </c>
+      <c r="B229">
+        <v>2</v>
+      </c>
+      <c r="C229" t="s">
+        <v>891</v>
+      </c>
+      <c r="D229" t="s">
+        <v>2967</v>
+      </c>
+      <c r="F229" t="s">
+        <v>6</v>
+      </c>
+      <c r="G229" t="s">
+        <v>37</v>
+      </c>
+      <c r="H229" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I229" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B230">
+        <v>2</v>
+      </c>
+      <c r="C230" t="s">
+        <v>891</v>
+      </c>
+      <c r="D230" t="s">
+        <v>2968</v>
+      </c>
+      <c r="F230" t="s">
+        <v>6</v>
+      </c>
+      <c r="G230" t="s">
+        <v>37</v>
+      </c>
+      <c r="H230" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I230" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>2925</v>
+      </c>
+      <c r="B231">
+        <v>2</v>
+      </c>
+      <c r="C231" t="s">
+        <v>891</v>
+      </c>
+      <c r="D231" t="s">
+        <v>2969</v>
+      </c>
+      <c r="F231" t="s">
+        <v>6</v>
+      </c>
+      <c r="G231" t="s">
+        <v>37</v>
+      </c>
+      <c r="H231" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I231" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B232">
+        <v>2</v>
+      </c>
+      <c r="C232" t="s">
+        <v>891</v>
+      </c>
+      <c r="D232" t="s">
+        <v>2970</v>
+      </c>
+      <c r="F232" t="s">
+        <v>6</v>
+      </c>
+      <c r="G232" t="s">
+        <v>37</v>
+      </c>
+      <c r="H232" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I232" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>2927</v>
+      </c>
+      <c r="B233">
+        <v>2</v>
+      </c>
+      <c r="C233" t="s">
+        <v>891</v>
+      </c>
+      <c r="D233" t="s">
+        <v>2971</v>
+      </c>
+      <c r="F233" t="s">
+        <v>6</v>
+      </c>
+      <c r="G233" t="s">
+        <v>37</v>
+      </c>
+      <c r="H233" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I233" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B234">
+        <v>2</v>
+      </c>
+      <c r="C234" t="s">
+        <v>891</v>
+      </c>
+      <c r="D234" t="s">
+        <v>2972</v>
+      </c>
+      <c r="F234" t="s">
+        <v>6</v>
+      </c>
+      <c r="G234" t="s">
+        <v>37</v>
+      </c>
+      <c r="H234" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I234" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>2929</v>
+      </c>
+      <c r="B235">
+        <v>2</v>
+      </c>
+      <c r="C235" t="s">
+        <v>891</v>
+      </c>
+      <c r="D235" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F235" t="s">
+        <v>6</v>
+      </c>
+      <c r="G235" t="s">
+        <v>37</v>
+      </c>
+      <c r="H235" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I235" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B236">
+        <v>2</v>
+      </c>
+      <c r="C236" t="s">
+        <v>891</v>
+      </c>
+      <c r="D236" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F236" t="s">
+        <v>6</v>
+      </c>
+      <c r="G236" t="s">
+        <v>37</v>
+      </c>
+      <c r="H236" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I236" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B237">
+        <v>2</v>
+      </c>
+      <c r="C237" t="s">
+        <v>891</v>
+      </c>
+      <c r="D237" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F237" t="s">
+        <v>6</v>
+      </c>
+      <c r="G237" t="s">
+        <v>37</v>
+      </c>
+      <c r="H237" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I237" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B238">
+        <v>2</v>
+      </c>
+      <c r="C238" t="s">
+        <v>891</v>
+      </c>
+      <c r="D238" t="s">
+        <v>2977</v>
+      </c>
+      <c r="F238" t="s">
+        <v>6</v>
+      </c>
+      <c r="G238" t="s">
+        <v>37</v>
+      </c>
+      <c r="H238" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I238" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B239">
+        <v>2</v>
+      </c>
+      <c r="C239" t="s">
+        <v>891</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>2987</v>
+      </c>
+      <c r="F239" t="s">
+        <v>6</v>
+      </c>
+      <c r="G239" t="s">
+        <v>37</v>
+      </c>
+      <c r="H239" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I239" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B240">
+        <v>2</v>
+      </c>
+      <c r="C240" t="s">
+        <v>891</v>
+      </c>
+      <c r="D240" t="s">
+        <v>2978</v>
+      </c>
+      <c r="F240" t="s">
+        <v>6</v>
+      </c>
+      <c r="G240" t="s">
+        <v>37</v>
+      </c>
+      <c r="H240" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I240" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B241">
+        <v>2</v>
+      </c>
+      <c r="C241" t="s">
+        <v>891</v>
+      </c>
+      <c r="D241" t="s">
+        <v>2979</v>
+      </c>
+      <c r="F241" t="s">
+        <v>6</v>
+      </c>
+      <c r="G241" t="s">
+        <v>37</v>
+      </c>
+      <c r="H241" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I241" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B242">
+        <v>2</v>
+      </c>
+      <c r="C242" t="s">
+        <v>891</v>
+      </c>
+      <c r="D242" t="s">
+        <v>2980</v>
+      </c>
+      <c r="F242" t="s">
+        <v>6</v>
+      </c>
+      <c r="G242" t="s">
+        <v>37</v>
+      </c>
+      <c r="H242" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I242" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B243">
+        <v>2</v>
+      </c>
+      <c r="C243" t="s">
+        <v>891</v>
+      </c>
+      <c r="D243" t="s">
+        <v>2981</v>
+      </c>
+      <c r="F243" t="s">
+        <v>6</v>
+      </c>
+      <c r="G243" t="s">
+        <v>37</v>
+      </c>
+      <c r="H243" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I243" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B244">
+        <v>2</v>
+      </c>
+      <c r="C244" t="s">
+        <v>891</v>
+      </c>
+      <c r="D244" t="s">
+        <v>2982</v>
+      </c>
+      <c r="F244" t="s">
+        <v>6</v>
+      </c>
+      <c r="G244" t="s">
+        <v>37</v>
+      </c>
+      <c r="H244" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I244" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B245">
+        <v>2</v>
+      </c>
+      <c r="C245" t="s">
+        <v>891</v>
+      </c>
+      <c r="D245" t="s">
+        <v>2983</v>
+      </c>
+      <c r="F245" t="s">
+        <v>6</v>
+      </c>
+      <c r="G245" t="s">
+        <v>37</v>
+      </c>
+      <c r="H245" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I245" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B246">
+        <v>2</v>
+      </c>
+      <c r="C246" t="s">
+        <v>891</v>
+      </c>
+      <c r="D246" t="s">
+        <v>2984</v>
+      </c>
+      <c r="F246" t="s">
+        <v>6</v>
+      </c>
+      <c r="G246" t="s">
+        <v>37</v>
+      </c>
+      <c r="H246" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I246" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B247">
+        <v>2</v>
+      </c>
+      <c r="C247" t="s">
+        <v>891</v>
+      </c>
+      <c r="D247" t="s">
+        <v>2985</v>
+      </c>
+      <c r="F247" t="s">
+        <v>6</v>
+      </c>
+      <c r="G247" t="s">
+        <v>37</v>
+      </c>
+      <c r="H247" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I247" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B248">
+        <v>2</v>
+      </c>
+      <c r="C248" t="s">
+        <v>891</v>
+      </c>
+      <c r="D248" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F248" t="s">
+        <v>6</v>
+      </c>
+      <c r="G248" t="s">
+        <v>37</v>
+      </c>
+      <c r="H248" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I248" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B249">
+        <v>2</v>
+      </c>
+      <c r="C249" t="s">
+        <v>891</v>
+      </c>
+      <c r="D249" t="s">
+        <v>2988</v>
+      </c>
+      <c r="F249" t="s">
+        <v>6</v>
+      </c>
+      <c r="G249" t="s">
+        <v>37</v>
+      </c>
+      <c r="H249" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I249" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B250">
+        <v>2</v>
+      </c>
+      <c r="C250" t="s">
+        <v>891</v>
+      </c>
+      <c r="D250" t="s">
+        <v>2989</v>
+      </c>
+      <c r="F250" t="s">
+        <v>6</v>
+      </c>
+      <c r="G250" t="s">
+        <v>37</v>
+      </c>
+      <c r="H250" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I250" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>2945</v>
+      </c>
+      <c r="B251">
+        <v>2</v>
+      </c>
+      <c r="C251" t="s">
+        <v>891</v>
+      </c>
+      <c r="D251" t="s">
+        <v>2990</v>
+      </c>
+      <c r="F251" t="s">
+        <v>6</v>
+      </c>
+      <c r="G251" t="s">
+        <v>37</v>
+      </c>
+      <c r="H251" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I251" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B252">
+        <v>2</v>
+      </c>
+      <c r="C252" t="s">
+        <v>891</v>
+      </c>
+      <c r="D252" t="s">
+        <v>2991</v>
+      </c>
+      <c r="F252" t="s">
+        <v>6</v>
+      </c>
+      <c r="G252" t="s">
+        <v>37</v>
+      </c>
+      <c r="H252" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I252" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B253">
+        <v>2</v>
+      </c>
+      <c r="C253" t="s">
+        <v>891</v>
+      </c>
+      <c r="D253" t="s">
+        <v>2992</v>
+      </c>
+      <c r="F253" t="s">
+        <v>6</v>
+      </c>
+      <c r="G253" t="s">
+        <v>37</v>
+      </c>
+      <c r="H253" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I253" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B254">
+        <v>2</v>
+      </c>
+      <c r="C254" t="s">
+        <v>891</v>
+      </c>
+      <c r="D254" t="s">
+        <v>2994</v>
+      </c>
+      <c r="F254" t="s">
+        <v>6</v>
+      </c>
+      <c r="G254" t="s">
+        <v>37</v>
+      </c>
+      <c r="H254" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I254" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B255">
+        <v>2</v>
+      </c>
+      <c r="C255" t="s">
+        <v>891</v>
+      </c>
+      <c r="D255" t="s">
+        <v>2993</v>
+      </c>
+      <c r="F255" t="s">
+        <v>6</v>
+      </c>
+      <c r="G255" t="s">
+        <v>37</v>
+      </c>
+      <c r="H255" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I255" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B256">
+        <v>2</v>
+      </c>
+      <c r="C256" t="s">
+        <v>891</v>
+      </c>
+      <c r="D256" t="s">
+        <v>2995</v>
+      </c>
+      <c r="F256" t="s">
+        <v>6</v>
+      </c>
+      <c r="G256" t="s">
+        <v>37</v>
+      </c>
+      <c r="H256" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I256" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B257">
+        <v>2</v>
+      </c>
+      <c r="C257" t="s">
+        <v>891</v>
+      </c>
+      <c r="D257" t="s">
+        <v>2996</v>
+      </c>
+      <c r="F257" t="s">
+        <v>6</v>
+      </c>
+      <c r="G257" t="s">
+        <v>37</v>
+      </c>
+      <c r="H257" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I257" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B258">
+        <v>2</v>
+      </c>
+      <c r="C258" t="s">
+        <v>891</v>
+      </c>
+      <c r="D258" t="s">
+        <v>2997</v>
+      </c>
+      <c r="F258" t="s">
+        <v>6</v>
+      </c>
+      <c r="G258" t="s">
+        <v>37</v>
+      </c>
+      <c r="H258" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I258" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B259">
+        <v>2</v>
+      </c>
+      <c r="C259" t="s">
+        <v>891</v>
+      </c>
+      <c r="D259" t="s">
+        <v>2998</v>
+      </c>
+      <c r="F259" t="s">
+        <v>6</v>
+      </c>
+      <c r="G259" t="s">
+        <v>37</v>
+      </c>
+      <c r="H259" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I259" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>2954</v>
+      </c>
+      <c r="B260">
+        <v>2</v>
+      </c>
+      <c r="C260" t="s">
+        <v>891</v>
+      </c>
+      <c r="D260" t="s">
+        <v>3003</v>
+      </c>
+      <c r="F260" t="s">
+        <v>6</v>
+      </c>
+      <c r="G260" t="s">
+        <v>37</v>
+      </c>
+      <c r="H260" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I260" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>2955</v>
+      </c>
+      <c r="B261">
+        <v>2</v>
+      </c>
+      <c r="C261" t="s">
+        <v>891</v>
+      </c>
+      <c r="D261" t="s">
+        <v>2999</v>
+      </c>
+      <c r="F261" t="s">
+        <v>6</v>
+      </c>
+      <c r="G261" t="s">
+        <v>37</v>
+      </c>
+      <c r="H261" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I261" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>2956</v>
+      </c>
+      <c r="B262">
+        <v>2</v>
+      </c>
+      <c r="C262" t="s">
+        <v>891</v>
+      </c>
+      <c r="D262" t="s">
+        <v>3000</v>
+      </c>
+      <c r="F262" t="s">
+        <v>6</v>
+      </c>
+      <c r="G262" t="s">
+        <v>37</v>
+      </c>
+      <c r="H262" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I262" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B263">
+        <v>2</v>
+      </c>
+      <c r="C263" t="s">
+        <v>891</v>
+      </c>
+      <c r="D263" t="s">
+        <v>3004</v>
+      </c>
+      <c r="F263" t="s">
+        <v>6</v>
+      </c>
+      <c r="G263" t="s">
+        <v>37</v>
+      </c>
+      <c r="H263" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I263" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B264">
+        <v>2</v>
+      </c>
+      <c r="C264" t="s">
+        <v>891</v>
+      </c>
+      <c r="D264" t="s">
+        <v>3001</v>
+      </c>
+      <c r="F264" t="s">
+        <v>6</v>
+      </c>
+      <c r="G264" t="s">
+        <v>37</v>
+      </c>
+      <c r="H264" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I264" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>2959</v>
+      </c>
+      <c r="B265">
+        <v>2</v>
+      </c>
+      <c r="C265" t="s">
+        <v>891</v>
+      </c>
+      <c r="D265" t="s">
+        <v>3002</v>
+      </c>
+      <c r="F265" t="s">
+        <v>6</v>
+      </c>
+      <c r="G265" t="s">
+        <v>37</v>
+      </c>
+      <c r="H265" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I265" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B266">
+        <v>2</v>
+      </c>
+      <c r="C266" t="s">
+        <v>891</v>
+      </c>
+      <c r="D266" t="s">
+        <v>3005</v>
+      </c>
+      <c r="F266" t="s">
+        <v>6</v>
+      </c>
+      <c r="G266" t="s">
+        <v>37</v>
+      </c>
+      <c r="H266" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I266" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B267">
+        <v>2</v>
+      </c>
+      <c r="C267" t="s">
+        <v>891</v>
+      </c>
+      <c r="D267" t="s">
+        <v>3006</v>
+      </c>
+      <c r="F267" t="s">
+        <v>6</v>
+      </c>
+      <c r="G267" t="s">
+        <v>37</v>
+      </c>
+      <c r="H267" t="s">
+        <v>2708</v>
+      </c>
+      <c r="I267" t="s">
+        <v>3008</v>
       </c>
     </row>
   </sheetData>
@@ -71005,18 +76049,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comments xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xsi:nil="true"/>
-    <TaxCatchAll xmlns="80b72feb-047f-4e13-841c-535f07286172" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D87D2D4B8525D945941C343DB74505E0" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4fde0782ba429c520ea89b375e2a9bbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xmlns:ns3="80b72feb-047f-4e13-841c-535f07286172" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9de2b51940fb1ddee93fed979ac2839f" ns2:_="" ns3:_="">
     <xsd:import namespace="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
@@ -71279,6 +76311,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comments xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xsi:nil="true"/>
+    <TaxCatchAll xmlns="80b72feb-047f-4e13-841c-535f07286172" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2F62DC0-0CC3-4554-AE40-B25C8DF78500}">
   <ds:schemaRefs>
@@ -71288,23 +76332,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFD6E32-6F0B-4771-89C7-827186DE1ED7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="80b72feb-047f-4e13-841c-535f07286172"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282722D5-1A18-4EBF-BE2A-C5B9E8FA6D2F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -71321,4 +76348,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFD6E32-6F0B-4771-89C7-827186DE1ED7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="80b72feb-047f-4e13-841c-535f07286172"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/SCAMP_data_dictionary.xlsx
+++ b/data/SCAMP_data_dictionary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon.sharepoint.com/sites/MBTteam/Shared Documents/04. Data Management/Data Dictionaries/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/cshen2_ic_ac_uk/Documents/SCAMP/Data dictionary/SCAMP_Shiny_dictionary_v0_1/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6294" documentId="11_C1B2DE3178FB31C93C31E9A30ADCF2804E5FDF90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9950614-F94A-4A99-B09A-1790B68BAC29}"/>
+  <xr:revisionPtr revIDLastSave="6295" documentId="11_C1B2DE3178FB31C93C31E9A30ADCF2804E5FDF90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E0764A8-F6B2-4447-B631-AE1900574592}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="792" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18058" uniqueCount="2963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18058" uniqueCount="2964">
   <si>
     <t>Instance</t>
   </si>
@@ -8935,6 +8935,9 @@
   </si>
   <si>
     <t>Decision Making Task</t>
+  </si>
+  <si>
+    <t>Key measure of probabilistic reversal learning</t>
   </si>
 </sst>
 </file>
@@ -66790,7 +66793,7 @@
         <v>866</v>
       </c>
       <c r="D1958" s="1" t="s">
-        <v>2960</v>
+        <v>2963</v>
       </c>
       <c r="H1958" s="1" t="s">
         <v>2469</v>
@@ -76078,6 +76081,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comments xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xsi:nil="true"/>
+    <TaxCatchAll xmlns="80b72feb-047f-4e13-841c-535f07286172" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D87D2D4B8525D945941C343DB74505E0" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4fde0782ba429c520ea89b375e2a9bbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xmlns:ns3="80b72feb-047f-4e13-841c-535f07286172" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9de2b51940fb1ddee93fed979ac2839f" ns2:_="" ns3:_="">
     <xsd:import namespace="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
@@ -76340,18 +76355,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comments xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xsi:nil="true"/>
-    <TaxCatchAll xmlns="80b72feb-047f-4e13-841c-535f07286172" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2F62DC0-0CC3-4554-AE40-B25C8DF78500}">
   <ds:schemaRefs>
@@ -76361,6 +76364,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFD6E32-6F0B-4771-89C7-827186DE1ED7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="80b72feb-047f-4e13-841c-535f07286172"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282722D5-1A18-4EBF-BE2A-C5B9E8FA6D2F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -76377,21 +76397,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFD6E32-6F0B-4771-89C7-827186DE1ED7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="80b72feb-047f-4e13-841c-535f07286172"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/SCAMP_data_dictionary.xlsx
+++ b/data/SCAMP_data_dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/cshen2_ic_ac_uk/Documents/SCAMP/Data dictionary/SCAMP_Shiny_dictionary_v0_1/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6295" documentId="11_C1B2DE3178FB31C93C31E9A30ADCF2804E5FDF90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E0764A8-F6B2-4447-B631-AE1900574592}"/>
+  <xr:revisionPtr revIDLastSave="6297" documentId="11_C1B2DE3178FB31C93C31E9A30ADCF2804E5FDF90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A6ACF80-EADD-4E80-9DFA-028C87E5677E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="792" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18058" uniqueCount="2964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18058" uniqueCount="2963">
   <si>
     <t>Instance</t>
   </si>
@@ -8926,9 +8926,6 @@
   </si>
   <si>
     <t>Reversal Learning Task</t>
-  </si>
-  <si>
-    <t>Key measyre of probabilistic reversal learning</t>
   </si>
   <si>
     <t>Key measure of economic decision making</t>
@@ -42123,7 +42120,7 @@
         <v>866</v>
       </c>
       <c r="D1120" s="1" t="s">
-        <v>2960</v>
+        <v>2962</v>
       </c>
       <c r="H1120" s="1" t="s">
         <v>6</v>
@@ -53967,7 +53964,7 @@
         <v>866</v>
       </c>
       <c r="D1504" s="1" t="s">
-        <v>2960</v>
+        <v>2962</v>
       </c>
       <c r="H1504" s="1" t="s">
         <v>6</v>
@@ -66793,7 +66790,7 @@
         <v>866</v>
       </c>
       <c r="D1958" s="1" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H1958" s="1" t="s">
         <v>2469</v>
@@ -66845,7 +66842,7 @@
         <v>866</v>
       </c>
       <c r="D1960" s="1" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="H1960" s="1" t="s">
         <v>2469</v>
@@ -66857,7 +66854,7 @@
         <v>868</v>
       </c>
       <c r="K1960" s="1" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
     </row>
   </sheetData>
@@ -76081,18 +76078,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comments xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xsi:nil="true"/>
-    <TaxCatchAll xmlns="80b72feb-047f-4e13-841c-535f07286172" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D87D2D4B8525D945941C343DB74505E0" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4fde0782ba429c520ea89b375e2a9bbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xmlns:ns3="80b72feb-047f-4e13-841c-535f07286172" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9de2b51940fb1ddee93fed979ac2839f" ns2:_="" ns3:_="">
     <xsd:import namespace="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
@@ -76355,6 +76340,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comments xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800" xsi:nil="true"/>
+    <TaxCatchAll xmlns="80b72feb-047f-4e13-841c-535f07286172" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e1c5d82-e03b-4d6b-97bb-a1180187c800">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2F62DC0-0CC3-4554-AE40-B25C8DF78500}">
   <ds:schemaRefs>
@@ -76364,23 +76361,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFD6E32-6F0B-4771-89C7-827186DE1ED7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="80b72feb-047f-4e13-841c-535f07286172"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282722D5-1A18-4EBF-BE2A-C5B9E8FA6D2F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -76397,4 +76377,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFD6E32-6F0B-4771-89C7-827186DE1ED7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="80b72feb-047f-4e13-841c-535f07286172"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1e1c5d82-e03b-4d6b-97bb-a1180187c800"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>